--- a/Istar_Development/Projects/BOL_Generation/Research/Empty MBOL & Supplemental BOL Draft.xlsx
+++ b/Istar_Development/Projects/BOL_Generation/Research/Empty MBOL & Supplemental BOL Draft.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Roman Sunstone Warehouse\Gal Access\BOL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Procomm\Documents\GitHub\Acumatica_Customizations_and_Packages\Istar_Development\Projects\BOL_Generation\Research\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFADE4B-5AB0-4DC7-AEE8-A4A515977F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF29C1D1-F843-4B48-9475-32DEB7E0727D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
+    <workbookView xWindow="4980" yWindow="4980" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
   </bookViews>
   <sheets>
     <sheet name="Master BOL" sheetId="3" r:id="rId1"/>
@@ -1675,6 +1675,324 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1714,12 +2032,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1813,15 +2125,6 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1849,352 +2152,400 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2218,12 +2569,6 @@
     <xf numFmtId="14" fontId="18" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2252,18 +2597,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2281,27 +2614,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2316,318 +2628,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4982,126 +4982,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="270" t="s">
+      <c r="A1" s="143" t="s">
         <v>237</v>
       </c>
-      <c r="B1" s="271"/>
-      <c r="C1" s="272" t="s">
+      <c r="B1" s="144"/>
+      <c r="C1" s="145" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="272"/>
-      <c r="E1" s="272"/>
-      <c r="F1" s="272"/>
-      <c r="G1" s="272"/>
-      <c r="H1" s="272"/>
-      <c r="I1" s="272"/>
-      <c r="J1" s="272"/>
-      <c r="K1" s="272"/>
-      <c r="L1" s="273" t="s">
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="146" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="274"/>
+      <c r="M1" s="147"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="249" t="s">
+      <c r="A2" s="140" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="250"/>
-      <c r="C2" s="250"/>
-      <c r="D2" s="250"/>
-      <c r="E2" s="250"/>
-      <c r="F2" s="250"/>
-      <c r="G2" s="250"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="275" t="s">
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="142"/>
+      <c r="I2" s="148" t="s">
         <v>232</v>
       </c>
-      <c r="J2" s="276"/>
-      <c r="K2" s="276"/>
-      <c r="L2" s="276"/>
-      <c r="M2" s="277"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="150"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="261" t="s">
+      <c r="A3" s="128" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="262"/>
-      <c r="C3" s="262"/>
-      <c r="D3" s="262"/>
-      <c r="E3" s="262"/>
-      <c r="F3" s="262"/>
-      <c r="G3" s="262"/>
-      <c r="H3" s="263"/>
-      <c r="I3" s="278"/>
-      <c r="J3" s="279"/>
-      <c r="K3" s="279"/>
-      <c r="L3" s="279"/>
-      <c r="M3" s="280"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="151"/>
+      <c r="J3" s="152"/>
+      <c r="K3" s="152"/>
+      <c r="L3" s="152"/>
+      <c r="M3" s="153"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="261" t="s">
+      <c r="A4" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="262"/>
-      <c r="C4" s="262"/>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="263"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="253"/>
-      <c r="K4" s="253"/>
-      <c r="L4" s="253"/>
-      <c r="M4" s="254"/>
+      <c r="B4" s="129"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="132"/>
+      <c r="K4" s="132"/>
+      <c r="L4" s="132"/>
+      <c r="M4" s="133"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="261" t="s">
+      <c r="A5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="262"/>
-      <c r="C5" s="262"/>
-      <c r="D5" s="262"/>
-      <c r="E5" s="262"/>
-      <c r="F5" s="262"/>
-      <c r="G5" s="262"/>
-      <c r="H5" s="263"/>
-      <c r="I5" s="252"/>
-      <c r="J5" s="253"/>
-      <c r="K5" s="253"/>
-      <c r="L5" s="253"/>
-      <c r="M5" s="254"/>
+      <c r="B5" s="129"/>
+      <c r="C5" s="129"/>
+      <c r="D5" s="129"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="131"/>
+      <c r="J5" s="132"/>
+      <c r="K5" s="132"/>
+      <c r="L5" s="132"/>
+      <c r="M5" s="133"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="267" t="s">
+      <c r="A6" s="137" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="268"/>
-      <c r="C6" s="268"/>
-      <c r="D6" s="268"/>
-      <c r="E6" s="268"/>
-      <c r="F6" s="269" t="s">
+      <c r="B6" s="138"/>
+      <c r="C6" s="138"/>
+      <c r="D6" s="138"/>
+      <c r="E6" s="138"/>
+      <c r="F6" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="269"/>
+      <c r="G6" s="139"/>
       <c r="H6" s="12"/>
-      <c r="I6" s="255"/>
-      <c r="J6" s="256"/>
-      <c r="K6" s="256"/>
-      <c r="L6" s="256"/>
-      <c r="M6" s="257"/>
+      <c r="I6" s="134"/>
+      <c r="J6" s="135"/>
+      <c r="K6" s="135"/>
+      <c r="L6" s="135"/>
+      <c r="M6" s="136"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="249" t="s">
+      <c r="A7" s="140" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="250"/>
-      <c r="C7" s="250"/>
-      <c r="D7" s="250"/>
-      <c r="E7" s="250"/>
-      <c r="F7" s="250"/>
-      <c r="G7" s="250"/>
-      <c r="H7" s="251"/>
+      <c r="B7" s="141"/>
+      <c r="C7" s="141"/>
+      <c r="D7" s="141"/>
+      <c r="E7" s="141"/>
+      <c r="F7" s="141"/>
+      <c r="G7" s="141"/>
+      <c r="H7" s="142"/>
       <c r="I7" s="53" t="s">
         <v>233</v>
       </c>
@@ -5114,37 +5114,37 @@
       <c r="M7" s="55"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="264" t="s">
+      <c r="A8" s="160" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="265"/>
-      <c r="C8" s="265"/>
-      <c r="D8" s="265"/>
-      <c r="E8" s="138" t="s">
+      <c r="B8" s="161"/>
+      <c r="C8" s="161"/>
+      <c r="D8" s="161"/>
+      <c r="E8" s="162" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="138"/>
-      <c r="G8" s="138"/>
-      <c r="H8" s="139"/>
-      <c r="I8" s="264" t="s">
+      <c r="F8" s="162"/>
+      <c r="G8" s="162"/>
+      <c r="H8" s="163"/>
+      <c r="I8" s="160" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="265"/>
-      <c r="K8" s="265"/>
-      <c r="L8" s="265"/>
-      <c r="M8" s="266"/>
+      <c r="J8" s="161"/>
+      <c r="K8" s="161"/>
+      <c r="L8" s="161"/>
+      <c r="M8" s="164"/>
     </row>
     <row r="9" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="264" t="s">
+      <c r="A9" s="160" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="265"/>
-      <c r="C9" s="265"/>
-      <c r="D9" s="265"/>
-      <c r="E9" s="265"/>
-      <c r="F9" s="265"/>
-      <c r="G9" s="265"/>
-      <c r="H9" s="266"/>
+      <c r="B9" s="161"/>
+      <c r="C9" s="161"/>
+      <c r="D9" s="161"/>
+      <c r="E9" s="161"/>
+      <c r="F9" s="161"/>
+      <c r="G9" s="161"/>
+      <c r="H9" s="164"/>
       <c r="I9" s="57" t="s">
         <v>74</v>
       </c>
@@ -5157,16 +5157,16 @@
       <c r="M9" s="13"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="264" t="s">
+      <c r="A10" s="160" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="265"/>
-      <c r="C10" s="265"/>
-      <c r="D10" s="265"/>
-      <c r="E10" s="265"/>
-      <c r="F10" s="265"/>
-      <c r="G10" s="265"/>
-      <c r="H10" s="266"/>
+      <c r="B10" s="161"/>
+      <c r="C10" s="161"/>
+      <c r="D10" s="161"/>
+      <c r="E10" s="161"/>
+      <c r="F10" s="161"/>
+      <c r="G10" s="161"/>
+      <c r="H10" s="164"/>
       <c r="I10" s="59" t="s">
         <v>234</v>
       </c>
@@ -5179,17 +5179,17 @@
       <c r="M10" s="61"/>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="246" t="s">
+      <c r="A11" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="247"/>
-      <c r="C11" s="247"/>
-      <c r="D11" s="247"/>
-      <c r="E11" s="247"/>
-      <c r="F11" s="248" t="s">
+      <c r="B11" s="155"/>
+      <c r="C11" s="155"/>
+      <c r="D11" s="155"/>
+      <c r="E11" s="155"/>
+      <c r="F11" s="156" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="248"/>
+      <c r="G11" s="156"/>
       <c r="H11" s="13"/>
       <c r="I11" s="62" t="s">
         <v>235</v>
@@ -5203,74 +5203,74 @@
       <c r="M11" s="64"/>
     </row>
     <row r="12" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="249" t="s">
+      <c r="A12" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="250"/>
-      <c r="C12" s="250"/>
-      <c r="D12" s="250"/>
-      <c r="E12" s="250"/>
-      <c r="F12" s="250"/>
-      <c r="G12" s="250"/>
-      <c r="H12" s="251"/>
-      <c r="I12" s="252"/>
-      <c r="J12" s="253"/>
-      <c r="K12" s="253"/>
-      <c r="L12" s="253"/>
-      <c r="M12" s="254"/>
+      <c r="B12" s="141"/>
+      <c r="C12" s="141"/>
+      <c r="D12" s="141"/>
+      <c r="E12" s="141"/>
+      <c r="F12" s="141"/>
+      <c r="G12" s="141"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="131"/>
+      <c r="J12" s="132"/>
+      <c r="K12" s="132"/>
+      <c r="L12" s="132"/>
+      <c r="M12" s="133"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="258" t="s">
+      <c r="A13" s="157" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="259"/>
-      <c r="C13" s="259"/>
-      <c r="D13" s="259"/>
-      <c r="E13" s="259"/>
-      <c r="F13" s="259"/>
-      <c r="G13" s="259"/>
-      <c r="H13" s="260"/>
-      <c r="I13" s="252"/>
-      <c r="J13" s="253"/>
-      <c r="K13" s="253"/>
-      <c r="L13" s="253"/>
-      <c r="M13" s="254"/>
+      <c r="B13" s="158"/>
+      <c r="C13" s="158"/>
+      <c r="D13" s="158"/>
+      <c r="E13" s="158"/>
+      <c r="F13" s="158"/>
+      <c r="G13" s="158"/>
+      <c r="H13" s="159"/>
+      <c r="I13" s="131"/>
+      <c r="J13" s="132"/>
+      <c r="K13" s="132"/>
+      <c r="L13" s="132"/>
+      <c r="M13" s="133"/>
     </row>
     <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="261" t="s">
+      <c r="A14" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="262"/>
-      <c r="C14" s="262"/>
-      <c r="D14" s="262"/>
-      <c r="E14" s="262"/>
-      <c r="F14" s="262"/>
-      <c r="G14" s="262"/>
-      <c r="H14" s="263"/>
-      <c r="I14" s="255"/>
-      <c r="J14" s="256"/>
-      <c r="K14" s="256"/>
-      <c r="L14" s="256"/>
-      <c r="M14" s="257"/>
+      <c r="B14" s="129"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="130"/>
+      <c r="I14" s="134"/>
+      <c r="J14" s="135"/>
+      <c r="K14" s="135"/>
+      <c r="L14" s="135"/>
+      <c r="M14" s="136"/>
     </row>
     <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="230" t="s">
+      <c r="A15" s="180" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="231"/>
-      <c r="C15" s="231"/>
-      <c r="D15" s="231"/>
-      <c r="E15" s="231"/>
-      <c r="F15" s="231"/>
-      <c r="G15" s="231"/>
-      <c r="H15" s="231"/>
-      <c r="I15" s="232" t="s">
+      <c r="B15" s="181"/>
+      <c r="C15" s="181"/>
+      <c r="D15" s="181"/>
+      <c r="E15" s="181"/>
+      <c r="F15" s="181"/>
+      <c r="G15" s="181"/>
+      <c r="H15" s="181"/>
+      <c r="I15" s="182" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="233"/>
-      <c r="K15" s="233"/>
-      <c r="L15" s="233"/>
-      <c r="M15" s="234"/>
+      <c r="J15" s="183"/>
+      <c r="K15" s="183"/>
+      <c r="L15" s="183"/>
+      <c r="M15" s="184"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="65" t="s">
@@ -5280,19 +5280,19 @@
       <c r="C16" s="66"/>
       <c r="D16" s="66"/>
       <c r="E16" s="66"/>
-      <c r="F16" s="130">
+      <c r="F16" s="236">
         <f>ADDRESS!I5</f>
         <v>59642884</v>
       </c>
-      <c r="G16" s="130"/>
-      <c r="H16" s="131"/>
-      <c r="I16" s="235" t="s">
+      <c r="G16" s="236"/>
+      <c r="H16" s="237"/>
+      <c r="I16" s="185" t="s">
         <v>61</v>
       </c>
-      <c r="J16" s="236"/>
-      <c r="K16" s="236"/>
-      <c r="L16" s="236"/>
-      <c r="M16" s="237"/>
+      <c r="J16" s="186"/>
+      <c r="K16" s="186"/>
+      <c r="L16" s="186"/>
+      <c r="M16" s="187"/>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="67"/>
@@ -5303,13 +5303,13 @@
       <c r="F17" s="68"/>
       <c r="G17" s="68"/>
       <c r="H17" s="69"/>
-      <c r="I17" s="238"/>
-      <c r="J17" s="239"/>
-      <c r="K17" s="240" t="s">
+      <c r="I17" s="188"/>
+      <c r="J17" s="189"/>
+      <c r="K17" s="190" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="240"/>
-      <c r="M17" s="241"/>
+      <c r="L17" s="190"/>
+      <c r="M17" s="191"/>
     </row>
     <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="67"/>
@@ -5320,323 +5320,323 @@
       <c r="F18" s="68"/>
       <c r="G18" s="68"/>
       <c r="H18" s="69"/>
-      <c r="I18" s="244" t="s">
+      <c r="I18" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="245"/>
-      <c r="K18" s="242"/>
-      <c r="L18" s="242"/>
-      <c r="M18" s="243"/>
+      <c r="J18" s="195"/>
+      <c r="K18" s="192"/>
+      <c r="L18" s="192"/>
+      <c r="M18" s="193"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="205" t="s">
+      <c r="A19" s="165" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="206"/>
-      <c r="C19" s="206"/>
-      <c r="D19" s="206"/>
-      <c r="E19" s="206"/>
-      <c r="F19" s="206"/>
-      <c r="G19" s="206"/>
-      <c r="H19" s="206"/>
-      <c r="I19" s="206"/>
-      <c r="J19" s="206"/>
-      <c r="K19" s="206"/>
-      <c r="L19" s="206"/>
-      <c r="M19" s="207"/>
+      <c r="B19" s="166"/>
+      <c r="C19" s="166"/>
+      <c r="D19" s="166"/>
+      <c r="E19" s="166"/>
+      <c r="F19" s="166"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="166"/>
+      <c r="I19" s="166"/>
+      <c r="J19" s="166"/>
+      <c r="K19" s="166"/>
+      <c r="L19" s="166"/>
+      <c r="M19" s="167"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="218" t="s">
+      <c r="A20" s="168" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="219"/>
-      <c r="C20" s="219"/>
-      <c r="D20" s="219"/>
-      <c r="E20" s="219" t="s">
+      <c r="B20" s="169"/>
+      <c r="C20" s="169"/>
+      <c r="D20" s="169"/>
+      <c r="E20" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="219" t="s">
+      <c r="F20" s="169" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="219"/>
-      <c r="H20" s="220" t="s">
+      <c r="G20" s="169"/>
+      <c r="H20" s="170" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="221"/>
-      <c r="J20" s="222" t="s">
+      <c r="I20" s="171"/>
+      <c r="J20" s="172" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="223"/>
-      <c r="L20" s="223"/>
-      <c r="M20" s="224"/>
+      <c r="K20" s="173"/>
+      <c r="L20" s="173"/>
+      <c r="M20" s="174"/>
     </row>
     <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="218"/>
-      <c r="B21" s="219"/>
-      <c r="C21" s="219"/>
-      <c r="D21" s="219"/>
-      <c r="E21" s="219"/>
-      <c r="F21" s="219"/>
-      <c r="G21" s="219"/>
-      <c r="H21" s="228" t="s">
+      <c r="A21" s="168"/>
+      <c r="B21" s="169"/>
+      <c r="C21" s="169"/>
+      <c r="D21" s="169"/>
+      <c r="E21" s="169"/>
+      <c r="F21" s="169"/>
+      <c r="G21" s="169"/>
+      <c r="H21" s="178" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="229"/>
-      <c r="J21" s="225"/>
-      <c r="K21" s="226"/>
-      <c r="L21" s="226"/>
-      <c r="M21" s="227"/>
+      <c r="I21" s="179"/>
+      <c r="J21" s="175"/>
+      <c r="K21" s="176"/>
+      <c r="L21" s="176"/>
+      <c r="M21" s="177"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="214"/>
-      <c r="B22" s="214"/>
-      <c r="C22" s="214"/>
-      <c r="D22" s="215"/>
+      <c r="A22" s="196"/>
+      <c r="B22" s="196"/>
+      <c r="C22" s="196"/>
+      <c r="D22" s="197"/>
       <c r="E22" s="10">
         <v>40</v>
       </c>
-      <c r="F22" s="333">
+      <c r="F22" s="198">
         <v>40</v>
       </c>
-      <c r="G22" s="333"/>
+      <c r="G22" s="198"/>
       <c r="H22" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="202"/>
-      <c r="K22" s="202"/>
-      <c r="L22" s="202"/>
-      <c r="M22" s="217"/>
+      <c r="J22" s="199"/>
+      <c r="K22" s="199"/>
+      <c r="L22" s="199"/>
+      <c r="M22" s="200"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="214"/>
-      <c r="B23" s="214"/>
-      <c r="C23" s="214"/>
-      <c r="D23" s="215"/>
+      <c r="A23" s="196"/>
+      <c r="B23" s="196"/>
+      <c r="C23" s="196"/>
+      <c r="D23" s="197"/>
       <c r="E23" s="10">
         <v>38</v>
       </c>
-      <c r="F23" s="333">
+      <c r="F23" s="198">
         <v>38</v>
       </c>
-      <c r="G23" s="333"/>
+      <c r="G23" s="198"/>
       <c r="H23" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="202"/>
-      <c r="K23" s="202"/>
-      <c r="L23" s="202"/>
-      <c r="M23" s="217"/>
+      <c r="J23" s="199"/>
+      <c r="K23" s="199"/>
+      <c r="L23" s="199"/>
+      <c r="M23" s="200"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="214"/>
-      <c r="B24" s="214"/>
-      <c r="C24" s="214"/>
-      <c r="D24" s="215"/>
+      <c r="A24" s="196"/>
+      <c r="B24" s="196"/>
+      <c r="C24" s="196"/>
+      <c r="D24" s="197"/>
       <c r="E24" s="10">
         <v>59</v>
       </c>
-      <c r="F24" s="333">
+      <c r="F24" s="198">
         <v>59</v>
       </c>
-      <c r="G24" s="333"/>
+      <c r="G24" s="198"/>
       <c r="H24" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I24" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="202"/>
-      <c r="K24" s="202"/>
-      <c r="L24" s="202"/>
-      <c r="M24" s="217"/>
+      <c r="J24" s="199"/>
+      <c r="K24" s="199"/>
+      <c r="L24" s="199"/>
+      <c r="M24" s="200"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="214"/>
-      <c r="B25" s="214"/>
-      <c r="C25" s="214"/>
-      <c r="D25" s="215"/>
+      <c r="A25" s="196"/>
+      <c r="B25" s="196"/>
+      <c r="C25" s="196"/>
+      <c r="D25" s="197"/>
       <c r="E25" s="10">
         <v>81</v>
       </c>
-      <c r="F25" s="333">
+      <c r="F25" s="198">
         <v>81</v>
       </c>
-      <c r="G25" s="333"/>
+      <c r="G25" s="198"/>
       <c r="H25" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I25" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="202"/>
-      <c r="K25" s="202"/>
-      <c r="L25" s="202"/>
-      <c r="M25" s="217"/>
+      <c r="J25" s="199"/>
+      <c r="K25" s="199"/>
+      <c r="L25" s="199"/>
+      <c r="M25" s="200"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="214"/>
-      <c r="B26" s="214"/>
-      <c r="C26" s="214"/>
-      <c r="D26" s="215"/>
+      <c r="A26" s="196"/>
+      <c r="B26" s="196"/>
+      <c r="C26" s="196"/>
+      <c r="D26" s="197"/>
       <c r="E26" s="10">
         <v>70</v>
       </c>
-      <c r="F26" s="333">
+      <c r="F26" s="198">
         <v>70</v>
       </c>
-      <c r="G26" s="333"/>
+      <c r="G26" s="198"/>
       <c r="H26" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I26" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="202"/>
-      <c r="K26" s="202"/>
-      <c r="L26" s="202"/>
-      <c r="M26" s="217"/>
+      <c r="J26" s="199"/>
+      <c r="K26" s="199"/>
+      <c r="L26" s="199"/>
+      <c r="M26" s="200"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="214"/>
-      <c r="B27" s="214"/>
-      <c r="C27" s="214"/>
-      <c r="D27" s="215"/>
+      <c r="A27" s="196"/>
+      <c r="B27" s="196"/>
+      <c r="C27" s="196"/>
+      <c r="D27" s="197"/>
       <c r="E27" s="10">
         <v>62</v>
       </c>
-      <c r="F27" s="333">
+      <c r="F27" s="198">
         <v>62</v>
       </c>
-      <c r="G27" s="333"/>
+      <c r="G27" s="198"/>
       <c r="H27" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I27" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J27" s="202"/>
-      <c r="K27" s="202"/>
-      <c r="L27" s="202"/>
-      <c r="M27" s="217"/>
+      <c r="J27" s="199"/>
+      <c r="K27" s="199"/>
+      <c r="L27" s="199"/>
+      <c r="M27" s="200"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="214"/>
-      <c r="B28" s="214"/>
-      <c r="C28" s="214"/>
-      <c r="D28" s="215"/>
+      <c r="A28" s="196"/>
+      <c r="B28" s="196"/>
+      <c r="C28" s="196"/>
+      <c r="D28" s="197"/>
       <c r="E28" s="10">
         <v>66</v>
       </c>
-      <c r="F28" s="333">
+      <c r="F28" s="198">
         <v>66</v>
       </c>
-      <c r="G28" s="333"/>
+      <c r="G28" s="198"/>
       <c r="H28" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J28" s="202"/>
-      <c r="K28" s="202"/>
-      <c r="L28" s="202"/>
-      <c r="M28" s="217"/>
+      <c r="J28" s="199"/>
+      <c r="K28" s="199"/>
+      <c r="L28" s="199"/>
+      <c r="M28" s="200"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="214"/>
-      <c r="B29" s="214"/>
-      <c r="C29" s="214"/>
-      <c r="D29" s="215"/>
+      <c r="A29" s="196"/>
+      <c r="B29" s="196"/>
+      <c r="C29" s="196"/>
+      <c r="D29" s="197"/>
       <c r="E29" s="10">
         <v>65</v>
       </c>
-      <c r="F29" s="333">
+      <c r="F29" s="198">
         <v>65</v>
       </c>
-      <c r="G29" s="333"/>
+      <c r="G29" s="198"/>
       <c r="H29" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I29" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J29" s="202"/>
-      <c r="K29" s="202"/>
-      <c r="L29" s="202"/>
-      <c r="M29" s="217"/>
+      <c r="J29" s="199"/>
+      <c r="K29" s="199"/>
+      <c r="L29" s="199"/>
+      <c r="M29" s="200"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="199" t="s">
+      <c r="A30" s="206" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="200"/>
-      <c r="C30" s="200"/>
-      <c r="D30" s="200"/>
+      <c r="B30" s="207"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="207"/>
       <c r="E30" s="16">
         <f>SUM(E22:E29,'Supplimental Master BOL'!E5:E25)</f>
         <v>1688</v>
       </c>
-      <c r="F30" s="201">
+      <c r="F30" s="208">
         <f>SUM(F22:G29,'Supplimental Master BOL'!F5:G25)</f>
         <v>1688</v>
       </c>
-      <c r="G30" s="202"/>
+      <c r="G30" s="199"/>
       <c r="H30" s="17"/>
       <c r="I30" s="17"/>
-      <c r="J30" s="203"/>
-      <c r="K30" s="203"/>
-      <c r="L30" s="203"/>
-      <c r="M30" s="204"/>
+      <c r="J30" s="209"/>
+      <c r="K30" s="209"/>
+      <c r="L30" s="209"/>
+      <c r="M30" s="210"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="205" t="s">
+      <c r="A31" s="165" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="206"/>
-      <c r="C31" s="206"/>
-      <c r="D31" s="206"/>
-      <c r="E31" s="206"/>
-      <c r="F31" s="206"/>
-      <c r="G31" s="206"/>
-      <c r="H31" s="206"/>
-      <c r="I31" s="206"/>
-      <c r="J31" s="206"/>
-      <c r="K31" s="206"/>
-      <c r="L31" s="206"/>
-      <c r="M31" s="207"/>
+      <c r="B31" s="166"/>
+      <c r="C31" s="166"/>
+      <c r="D31" s="166"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="166"/>
+      <c r="G31" s="166"/>
+      <c r="H31" s="166"/>
+      <c r="I31" s="166"/>
+      <c r="J31" s="166"/>
+      <c r="K31" s="166"/>
+      <c r="L31" s="166"/>
+      <c r="M31" s="167"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="208" t="s">
+      <c r="A32" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="209"/>
-      <c r="C32" s="209" t="s">
+      <c r="B32" s="212"/>
+      <c r="C32" s="212" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="209"/>
-      <c r="E32" s="210" t="s">
+      <c r="D32" s="212"/>
+      <c r="E32" s="213" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="211" t="s">
+      <c r="F32" s="214" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="212" t="s">
+      <c r="G32" s="215" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="212"/>
-      <c r="I32" s="212"/>
-      <c r="J32" s="212"/>
-      <c r="K32" s="212"/>
-      <c r="L32" s="209" t="s">
+      <c r="H32" s="215"/>
+      <c r="I32" s="215"/>
+      <c r="J32" s="215"/>
+      <c r="K32" s="215"/>
+      <c r="L32" s="212" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="213"/>
+      <c r="M32" s="216"/>
     </row>
     <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="18" t="s">
@@ -5651,15 +5651,15 @@
       <c r="D33" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="210"/>
-      <c r="F33" s="211"/>
-      <c r="G33" s="198" t="s">
+      <c r="E33" s="213"/>
+      <c r="F33" s="214"/>
+      <c r="G33" s="201" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="198"/>
-      <c r="I33" s="198"/>
-      <c r="J33" s="198"/>
-      <c r="K33" s="198"/>
+      <c r="H33" s="201"/>
+      <c r="I33" s="201"/>
+      <c r="J33" s="201"/>
+      <c r="K33" s="201"/>
       <c r="L33" s="20" t="s">
         <v>14</v>
       </c>
@@ -5684,13 +5684,13 @@
         <v>6698</v>
       </c>
       <c r="F34" s="14"/>
-      <c r="G34" s="171" t="s">
+      <c r="G34" s="202" t="s">
         <v>70</v>
       </c>
-      <c r="H34" s="172"/>
-      <c r="I34" s="172"/>
-      <c r="J34" s="172"/>
-      <c r="K34" s="173"/>
+      <c r="H34" s="203"/>
+      <c r="I34" s="203"/>
+      <c r="J34" s="203"/>
+      <c r="K34" s="204"/>
       <c r="L34" s="24"/>
       <c r="M34" s="25"/>
     </row>
@@ -5701,11 +5701,11 @@
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="26"/>
-      <c r="G35" s="171"/>
-      <c r="H35" s="172"/>
-      <c r="I35" s="172"/>
-      <c r="J35" s="172"/>
-      <c r="K35" s="173"/>
+      <c r="G35" s="202"/>
+      <c r="H35" s="203"/>
+      <c r="I35" s="203"/>
+      <c r="J35" s="203"/>
+      <c r="K35" s="204"/>
       <c r="L35" s="24"/>
       <c r="M35" s="25"/>
     </row>
@@ -5716,11 +5716,11 @@
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="26"/>
-      <c r="G36" s="171"/>
-      <c r="H36" s="172"/>
-      <c r="I36" s="172"/>
-      <c r="J36" s="172"/>
-      <c r="K36" s="173"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="203"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="203"/>
+      <c r="K36" s="204"/>
       <c r="L36" s="24"/>
       <c r="M36" s="25"/>
     </row>
@@ -5731,19 +5731,19 @@
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="26"/>
-      <c r="G37" s="171"/>
-      <c r="H37" s="172"/>
-      <c r="I37" s="172"/>
-      <c r="J37" s="172"/>
-      <c r="K37" s="173"/>
+      <c r="G37" s="202"/>
+      <c r="H37" s="203"/>
+      <c r="I37" s="203"/>
+      <c r="J37" s="203"/>
+      <c r="K37" s="204"/>
       <c r="L37" s="24"/>
       <c r="M37" s="25"/>
-      <c r="Q37" s="196"/>
-      <c r="R37" s="196"/>
+      <c r="Q37" s="205"/>
+      <c r="R37" s="205"/>
       <c r="S37" s="27"/>
-      <c r="T37" s="195"/>
-      <c r="U37" s="195"/>
-      <c r="V37" s="195"/>
+      <c r="T37" s="229"/>
+      <c r="U37" s="229"/>
+      <c r="V37" s="229"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A38" s="22"/>
@@ -5752,19 +5752,19 @@
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="26"/>
-      <c r="G38" s="171"/>
-      <c r="H38" s="172"/>
-      <c r="I38" s="172"/>
-      <c r="J38" s="172"/>
-      <c r="K38" s="173"/>
+      <c r="G38" s="202"/>
+      <c r="H38" s="203"/>
+      <c r="I38" s="203"/>
+      <c r="J38" s="203"/>
+      <c r="K38" s="204"/>
       <c r="L38" s="24"/>
       <c r="M38" s="29"/>
-      <c r="Q38" s="196"/>
-      <c r="R38" s="196"/>
+      <c r="Q38" s="205"/>
+      <c r="R38" s="205"/>
       <c r="S38" s="27"/>
-      <c r="T38" s="195"/>
-      <c r="U38" s="195"/>
-      <c r="V38" s="195"/>
+      <c r="T38" s="229"/>
+      <c r="U38" s="229"/>
+      <c r="V38" s="229"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A39" s="22"/>
@@ -5773,19 +5773,19 @@
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="26"/>
-      <c r="G39" s="171"/>
-      <c r="H39" s="172"/>
-      <c r="I39" s="172"/>
-      <c r="J39" s="172"/>
-      <c r="K39" s="173"/>
+      <c r="G39" s="202"/>
+      <c r="H39" s="203"/>
+      <c r="I39" s="203"/>
+      <c r="J39" s="203"/>
+      <c r="K39" s="204"/>
       <c r="L39" s="24"/>
       <c r="M39" s="29"/>
       <c r="Q39" s="30"/>
       <c r="R39" s="30"/>
-      <c r="S39" s="197"/>
-      <c r="T39" s="195"/>
-      <c r="U39" s="195"/>
-      <c r="V39" s="195"/>
+      <c r="S39" s="230"/>
+      <c r="T39" s="229"/>
+      <c r="U39" s="229"/>
+      <c r="V39" s="229"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A40" s="22"/>
@@ -5794,19 +5794,19 @@
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="26"/>
-      <c r="G40" s="171"/>
-      <c r="H40" s="172"/>
-      <c r="I40" s="172"/>
-      <c r="J40" s="172"/>
-      <c r="K40" s="173"/>
+      <c r="G40" s="202"/>
+      <c r="H40" s="203"/>
+      <c r="I40" s="203"/>
+      <c r="J40" s="203"/>
+      <c r="K40" s="204"/>
       <c r="L40" s="24"/>
       <c r="M40" s="25"/>
       <c r="Q40" s="30"/>
       <c r="R40" s="30"/>
-      <c r="S40" s="197"/>
-      <c r="T40" s="195"/>
-      <c r="U40" s="195"/>
-      <c r="V40" s="195"/>
+      <c r="S40" s="230"/>
+      <c r="T40" s="229"/>
+      <c r="U40" s="229"/>
+      <c r="V40" s="229"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A41" s="22"/>
@@ -5815,11 +5815,11 @@
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="26"/>
-      <c r="G41" s="171"/>
-      <c r="H41" s="172"/>
-      <c r="I41" s="172"/>
-      <c r="J41" s="172"/>
-      <c r="K41" s="173"/>
+      <c r="G41" s="202"/>
+      <c r="H41" s="203"/>
+      <c r="I41" s="203"/>
+      <c r="J41" s="203"/>
+      <c r="K41" s="204"/>
       <c r="L41" s="24"/>
       <c r="M41" s="25"/>
     </row>
@@ -5836,296 +5836,296 @@
         <v>1688</v>
       </c>
       <c r="F42" s="34"/>
-      <c r="G42" s="174" t="s">
+      <c r="G42" s="275" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="175"/>
-      <c r="I42" s="175"/>
-      <c r="J42" s="175"/>
-      <c r="K42" s="176"/>
+      <c r="H42" s="276"/>
+      <c r="I42" s="276"/>
+      <c r="J42" s="276"/>
+      <c r="K42" s="277"/>
       <c r="L42" s="35"/>
       <c r="M42" s="36"/>
     </row>
     <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="148" t="s">
+      <c r="A43" s="252" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="149"/>
-      <c r="C43" s="149"/>
-      <c r="D43" s="149"/>
-      <c r="E43" s="149"/>
-      <c r="F43" s="149"/>
-      <c r="G43" s="149"/>
-      <c r="H43" s="150"/>
-      <c r="I43" s="177" t="s">
+      <c r="B43" s="253"/>
+      <c r="C43" s="253"/>
+      <c r="D43" s="253"/>
+      <c r="E43" s="253"/>
+      <c r="F43" s="253"/>
+      <c r="G43" s="253"/>
+      <c r="H43" s="254"/>
+      <c r="I43" s="278" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="178"/>
-      <c r="K43" s="178"/>
-      <c r="L43" s="178"/>
-      <c r="M43" s="179"/>
+      <c r="J43" s="279"/>
+      <c r="K43" s="279"/>
+      <c r="L43" s="279"/>
+      <c r="M43" s="280"/>
     </row>
     <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="151"/>
-      <c r="B44" s="152"/>
-      <c r="C44" s="152"/>
-      <c r="D44" s="152"/>
-      <c r="E44" s="152"/>
-      <c r="F44" s="152"/>
-      <c r="G44" s="152"/>
-      <c r="H44" s="153"/>
-      <c r="I44" s="180"/>
-      <c r="J44" s="181"/>
-      <c r="K44" s="181"/>
-      <c r="L44" s="181"/>
-      <c r="M44" s="182"/>
+      <c r="A44" s="255"/>
+      <c r="B44" s="256"/>
+      <c r="C44" s="256"/>
+      <c r="D44" s="256"/>
+      <c r="E44" s="256"/>
+      <c r="F44" s="256"/>
+      <c r="G44" s="256"/>
+      <c r="H44" s="257"/>
+      <c r="I44" s="281"/>
+      <c r="J44" s="282"/>
+      <c r="K44" s="282"/>
+      <c r="L44" s="282"/>
+      <c r="M44" s="283"/>
     </row>
     <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="183" t="s">
+      <c r="A45" s="217" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="184"/>
-      <c r="C45" s="184"/>
-      <c r="D45" s="184"/>
-      <c r="E45" s="184"/>
-      <c r="F45" s="184"/>
-      <c r="G45" s="184"/>
-      <c r="H45" s="185"/>
-      <c r="I45" s="186" t="s">
+      <c r="B45" s="218"/>
+      <c r="C45" s="218"/>
+      <c r="D45" s="218"/>
+      <c r="E45" s="218"/>
+      <c r="F45" s="218"/>
+      <c r="G45" s="218"/>
+      <c r="H45" s="219"/>
+      <c r="I45" s="220" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="187"/>
-      <c r="K45" s="187"/>
-      <c r="L45" s="187"/>
-      <c r="M45" s="188"/>
+      <c r="J45" s="221"/>
+      <c r="K45" s="221"/>
+      <c r="L45" s="221"/>
+      <c r="M45" s="222"/>
     </row>
     <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="183" t="s">
+      <c r="A46" s="217" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="184"/>
-      <c r="C46" s="184"/>
-      <c r="D46" s="184"/>
-      <c r="E46" s="184"/>
-      <c r="F46" s="184"/>
-      <c r="G46" s="184"/>
-      <c r="H46" s="185"/>
-      <c r="I46" s="186"/>
-      <c r="J46" s="187"/>
-      <c r="K46" s="187"/>
-      <c r="L46" s="187"/>
-      <c r="M46" s="188"/>
+      <c r="B46" s="218"/>
+      <c r="C46" s="218"/>
+      <c r="D46" s="218"/>
+      <c r="E46" s="218"/>
+      <c r="F46" s="218"/>
+      <c r="G46" s="218"/>
+      <c r="H46" s="219"/>
+      <c r="I46" s="220"/>
+      <c r="J46" s="221"/>
+      <c r="K46" s="221"/>
+      <c r="L46" s="221"/>
+      <c r="M46" s="222"/>
     </row>
     <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="189"/>
-      <c r="B47" s="190"/>
-      <c r="C47" s="190"/>
-      <c r="D47" s="190"/>
-      <c r="E47" s="190"/>
-      <c r="F47" s="190"/>
-      <c r="G47" s="190"/>
-      <c r="H47" s="191"/>
-      <c r="I47" s="192" t="s">
+      <c r="A47" s="223"/>
+      <c r="B47" s="224"/>
+      <c r="C47" s="224"/>
+      <c r="D47" s="224"/>
+      <c r="E47" s="224"/>
+      <c r="F47" s="224"/>
+      <c r="G47" s="224"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="226" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="193"/>
-      <c r="K47" s="193"/>
-      <c r="L47" s="193"/>
-      <c r="M47" s="194"/>
+      <c r="J47" s="227"/>
+      <c r="K47" s="227"/>
+      <c r="L47" s="227"/>
+      <c r="M47" s="228"/>
     </row>
     <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="145" t="s">
+      <c r="A48" s="249" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="146"/>
-      <c r="C48" s="146"/>
-      <c r="D48" s="146"/>
-      <c r="E48" s="146"/>
-      <c r="F48" s="146"/>
-      <c r="G48" s="146"/>
-      <c r="H48" s="146"/>
-      <c r="I48" s="146"/>
-      <c r="J48" s="146"/>
-      <c r="K48" s="146"/>
-      <c r="L48" s="146"/>
-      <c r="M48" s="147"/>
+      <c r="B48" s="250"/>
+      <c r="C48" s="250"/>
+      <c r="D48" s="250"/>
+      <c r="E48" s="250"/>
+      <c r="F48" s="250"/>
+      <c r="G48" s="250"/>
+      <c r="H48" s="250"/>
+      <c r="I48" s="250"/>
+      <c r="J48" s="250"/>
+      <c r="K48" s="250"/>
+      <c r="L48" s="250"/>
+      <c r="M48" s="251"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="148" t="s">
+      <c r="A49" s="252" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="149"/>
-      <c r="C49" s="149"/>
-      <c r="D49" s="149"/>
-      <c r="E49" s="149"/>
-      <c r="F49" s="149"/>
-      <c r="G49" s="149"/>
-      <c r="H49" s="150"/>
-      <c r="I49" s="156" t="s">
+      <c r="B49" s="253"/>
+      <c r="C49" s="253"/>
+      <c r="D49" s="253"/>
+      <c r="E49" s="253"/>
+      <c r="F49" s="253"/>
+      <c r="G49" s="253"/>
+      <c r="H49" s="254"/>
+      <c r="I49" s="260" t="s">
         <v>40</v>
       </c>
-      <c r="J49" s="157"/>
-      <c r="K49" s="157"/>
-      <c r="L49" s="157"/>
-      <c r="M49" s="158"/>
+      <c r="J49" s="261"/>
+      <c r="K49" s="261"/>
+      <c r="L49" s="261"/>
+      <c r="M49" s="262"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="151"/>
-      <c r="B50" s="152"/>
-      <c r="C50" s="152"/>
-      <c r="D50" s="152"/>
-      <c r="E50" s="152"/>
-      <c r="F50" s="152"/>
-      <c r="G50" s="152"/>
-      <c r="H50" s="153"/>
-      <c r="I50" s="159"/>
-      <c r="J50" s="160"/>
-      <c r="K50" s="160"/>
-      <c r="L50" s="160"/>
-      <c r="M50" s="161"/>
+      <c r="A50" s="255"/>
+      <c r="B50" s="256"/>
+      <c r="C50" s="256"/>
+      <c r="D50" s="256"/>
+      <c r="E50" s="256"/>
+      <c r="F50" s="256"/>
+      <c r="G50" s="256"/>
+      <c r="H50" s="257"/>
+      <c r="I50" s="263"/>
+      <c r="J50" s="264"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="265"/>
     </row>
     <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="154"/>
-      <c r="B51" s="155"/>
-      <c r="C51" s="155"/>
-      <c r="D51" s="155"/>
-      <c r="E51" s="152"/>
-      <c r="F51" s="152"/>
-      <c r="G51" s="152"/>
-      <c r="H51" s="153"/>
-      <c r="I51" s="162" t="s">
+      <c r="A51" s="258"/>
+      <c r="B51" s="259"/>
+      <c r="C51" s="259"/>
+      <c r="D51" s="259"/>
+      <c r="E51" s="256"/>
+      <c r="F51" s="256"/>
+      <c r="G51" s="256"/>
+      <c r="H51" s="257"/>
+      <c r="I51" s="266" t="s">
         <v>41</v>
       </c>
-      <c r="J51" s="163"/>
-      <c r="K51" s="164"/>
-      <c r="L51" s="164"/>
-      <c r="M51" s="165"/>
+      <c r="J51" s="267"/>
+      <c r="K51" s="268"/>
+      <c r="L51" s="268"/>
+      <c r="M51" s="269"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="166" t="s">
+      <c r="A52" s="270" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="167"/>
-      <c r="C52" s="167"/>
-      <c r="D52" s="167"/>
+      <c r="B52" s="271"/>
+      <c r="C52" s="271"/>
+      <c r="D52" s="271"/>
       <c r="E52" s="37" t="s">
         <v>44</v>
       </c>
       <c r="F52" s="38"/>
-      <c r="G52" s="168" t="s">
+      <c r="G52" s="272" t="s">
         <v>45</v>
       </c>
-      <c r="H52" s="168"/>
-      <c r="I52" s="168"/>
-      <c r="J52" s="169"/>
-      <c r="K52" s="167" t="s">
+      <c r="H52" s="272"/>
+      <c r="I52" s="272"/>
+      <c r="J52" s="273"/>
+      <c r="K52" s="271" t="s">
         <v>50</v>
       </c>
-      <c r="L52" s="167"/>
-      <c r="M52" s="170"/>
+      <c r="L52" s="271"/>
+      <c r="M52" s="274"/>
     </row>
     <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="132" t="s">
+      <c r="A53" s="238" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="133"/>
-      <c r="C53" s="133"/>
-      <c r="D53" s="133"/>
+      <c r="B53" s="239"/>
+      <c r="C53" s="239"/>
+      <c r="D53" s="239"/>
       <c r="E53" s="39"/>
       <c r="F53" s="40"/>
       <c r="G53" s="40"/>
       <c r="H53" s="40"/>
       <c r="I53" s="40"/>
       <c r="J53" s="41"/>
-      <c r="K53" s="133" t="s">
+      <c r="K53" s="239" t="s">
         <v>52</v>
       </c>
-      <c r="L53" s="133"/>
-      <c r="M53" s="134"/>
+      <c r="L53" s="239"/>
+      <c r="M53" s="240"/>
     </row>
     <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="132"/>
-      <c r="B54" s="133"/>
-      <c r="C54" s="133"/>
-      <c r="D54" s="133"/>
-      <c r="E54" s="135" t="s">
+      <c r="A54" s="238"/>
+      <c r="B54" s="239"/>
+      <c r="C54" s="239"/>
+      <c r="D54" s="239"/>
+      <c r="E54" s="241" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="136"/>
+      <c r="F54" s="242"/>
       <c r="G54" s="42"/>
-      <c r="H54" s="125" t="s">
+      <c r="H54" s="231" t="s">
         <v>46</v>
       </c>
-      <c r="I54" s="125"/>
-      <c r="J54" s="126"/>
-      <c r="K54" s="133"/>
-      <c r="L54" s="133"/>
-      <c r="M54" s="134"/>
+      <c r="I54" s="231"/>
+      <c r="J54" s="232"/>
+      <c r="K54" s="239"/>
+      <c r="L54" s="239"/>
+      <c r="M54" s="240"/>
     </row>
     <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="132"/>
-      <c r="B55" s="133"/>
-      <c r="C55" s="133"/>
-      <c r="D55" s="133"/>
-      <c r="E55" s="135" t="s">
+      <c r="A55" s="238"/>
+      <c r="B55" s="239"/>
+      <c r="C55" s="239"/>
+      <c r="D55" s="239"/>
+      <c r="E55" s="241" t="s">
         <v>47</v>
       </c>
-      <c r="F55" s="136"/>
-      <c r="G55" s="136"/>
-      <c r="H55" s="125" t="s">
+      <c r="F55" s="242"/>
+      <c r="G55" s="242"/>
+      <c r="H55" s="231" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="125"/>
-      <c r="J55" s="126"/>
-      <c r="K55" s="133"/>
-      <c r="L55" s="133"/>
-      <c r="M55" s="134"/>
+      <c r="I55" s="231"/>
+      <c r="J55" s="232"/>
+      <c r="K55" s="239"/>
+      <c r="L55" s="239"/>
+      <c r="M55" s="240"/>
     </row>
     <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="137"/>
-      <c r="B56" s="138"/>
-      <c r="C56" s="138"/>
-      <c r="D56" s="139"/>
-      <c r="E56" s="135"/>
-      <c r="F56" s="136"/>
-      <c r="G56" s="136"/>
-      <c r="H56" s="125"/>
-      <c r="I56" s="125"/>
-      <c r="J56" s="126"/>
-      <c r="K56" s="143" t="s">
+      <c r="A56" s="243"/>
+      <c r="B56" s="162"/>
+      <c r="C56" s="162"/>
+      <c r="D56" s="163"/>
+      <c r="E56" s="241"/>
+      <c r="F56" s="242"/>
+      <c r="G56" s="242"/>
+      <c r="H56" s="231"/>
+      <c r="I56" s="231"/>
+      <c r="J56" s="232"/>
+      <c r="K56" s="247" t="s">
         <v>51</v>
       </c>
-      <c r="L56" s="143"/>
-      <c r="M56" s="144"/>
+      <c r="L56" s="247"/>
+      <c r="M56" s="248"/>
     </row>
     <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="137"/>
-      <c r="B57" s="138"/>
-      <c r="C57" s="138"/>
-      <c r="D57" s="139"/>
-      <c r="E57" s="135"/>
-      <c r="F57" s="136"/>
+      <c r="A57" s="243"/>
+      <c r="B57" s="162"/>
+      <c r="C57" s="162"/>
+      <c r="D57" s="163"/>
+      <c r="E57" s="241"/>
+      <c r="F57" s="242"/>
       <c r="G57" s="42"/>
-      <c r="H57" s="125" t="s">
+      <c r="H57" s="231" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="125"/>
-      <c r="J57" s="126"/>
+      <c r="I57" s="231"/>
+      <c r="J57" s="232"/>
       <c r="K57" s="43"/>
       <c r="L57" s="44"/>
       <c r="M57" s="45"/>
     </row>
     <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="140"/>
-      <c r="B58" s="141"/>
-      <c r="C58" s="141"/>
-      <c r="D58" s="142"/>
-      <c r="E58" s="127"/>
-      <c r="F58" s="128"/>
-      <c r="G58" s="128"/>
-      <c r="H58" s="128"/>
-      <c r="I58" s="128"/>
-      <c r="J58" s="129"/>
+      <c r="A58" s="244"/>
+      <c r="B58" s="245"/>
+      <c r="C58" s="245"/>
+      <c r="D58" s="246"/>
+      <c r="E58" s="233"/>
+      <c r="F58" s="234"/>
+      <c r="G58" s="234"/>
+      <c r="H58" s="234"/>
+      <c r="I58" s="234"/>
+      <c r="J58" s="235"/>
       <c r="K58" s="46"/>
       <c r="L58" s="47"/>
       <c r="M58" s="48"/>
@@ -6144,94 +6144,6 @@
     </row>
   </sheetData>
   <mergeCells count="112">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="I4:M6"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:M3"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="I12:M14"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="I8:M8"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:G21"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="J20:M21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="I16:M16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:M18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="G33:K33"/>
-    <mergeCell ref="G34:K34"/>
-    <mergeCell ref="G35:K35"/>
-    <mergeCell ref="G36:K36"/>
-    <mergeCell ref="G37:K37"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="A31:M31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="I45:M46"/>
-    <mergeCell ref="A46:H47"/>
-    <mergeCell ref="I47:M47"/>
-    <mergeCell ref="T37:V37"/>
-    <mergeCell ref="G38:K38"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="T38:V38"/>
-    <mergeCell ref="G39:K39"/>
-    <mergeCell ref="S39:S40"/>
-    <mergeCell ref="T39:V40"/>
-    <mergeCell ref="G40:K40"/>
     <mergeCell ref="H57:J57"/>
     <mergeCell ref="E58:J58"/>
     <mergeCell ref="F16:H16"/>
@@ -6256,6 +6168,94 @@
     <mergeCell ref="G42:K42"/>
     <mergeCell ref="A43:H44"/>
     <mergeCell ref="I43:M44"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="I45:M46"/>
+    <mergeCell ref="A46:H47"/>
+    <mergeCell ref="I47:M47"/>
+    <mergeCell ref="T37:V37"/>
+    <mergeCell ref="G38:K38"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="T38:V38"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="S39:S40"/>
+    <mergeCell ref="T39:V40"/>
+    <mergeCell ref="G40:K40"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="G34:K34"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:G21"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J20:M21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="I16:M16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:M18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="I12:M14"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="I4:M6"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="I2:M3"/>
+    <mergeCell ref="A3:H3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.26" top="0.52" bottom="0.56000000000000005" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6976,1102 +6976,1102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="270" t="s">
+      <c r="A1" s="143" t="s">
         <v>237</v>
       </c>
-      <c r="B1" s="271"/>
-      <c r="C1" s="272" t="s">
+      <c r="B1" s="144"/>
+      <c r="C1" s="145" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="272"/>
-      <c r="E1" s="272"/>
-      <c r="F1" s="272"/>
-      <c r="G1" s="272"/>
-      <c r="H1" s="272"/>
-      <c r="I1" s="272"/>
-      <c r="J1" s="272"/>
-      <c r="K1" s="272"/>
-      <c r="L1" s="273" t="s">
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="146" t="s">
         <v>63</v>
       </c>
-      <c r="M1" s="274"/>
+      <c r="M1" s="147"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="205" t="s">
+      <c r="A2" s="165" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="206"/>
-      <c r="C2" s="206"/>
-      <c r="D2" s="206"/>
-      <c r="E2" s="206"/>
-      <c r="F2" s="206"/>
-      <c r="G2" s="206"/>
-      <c r="H2" s="206"/>
-      <c r="I2" s="206"/>
-      <c r="J2" s="206"/>
-      <c r="K2" s="206"/>
-      <c r="L2" s="206"/>
-      <c r="M2" s="207"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="166"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="166"/>
+      <c r="G2" s="166"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
+      <c r="L2" s="166"/>
+      <c r="M2" s="167"/>
     </row>
     <row r="3" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="218" t="s">
+      <c r="A3" s="168" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="219"/>
-      <c r="C3" s="219"/>
-      <c r="D3" s="219"/>
-      <c r="E3" s="219" t="s">
+      <c r="B3" s="169"/>
+      <c r="C3" s="169"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="219" t="s">
+      <c r="F3" s="169" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="219"/>
-      <c r="H3" s="220" t="s">
+      <c r="G3" s="169"/>
+      <c r="H3" s="170" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="221"/>
-      <c r="J3" s="222" t="s">
+      <c r="I3" s="171"/>
+      <c r="J3" s="172" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="223"/>
-      <c r="L3" s="223"/>
-      <c r="M3" s="224"/>
+      <c r="K3" s="173"/>
+      <c r="L3" s="173"/>
+      <c r="M3" s="174"/>
     </row>
     <row r="4" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="218"/>
-      <c r="B4" s="219"/>
-      <c r="C4" s="219"/>
-      <c r="D4" s="219"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="219"/>
-      <c r="G4" s="219"/>
-      <c r="H4" s="228" t="s">
+      <c r="A4" s="168"/>
+      <c r="B4" s="169"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="169"/>
+      <c r="G4" s="169"/>
+      <c r="H4" s="178" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="229"/>
-      <c r="J4" s="225"/>
-      <c r="K4" s="226"/>
-      <c r="L4" s="226"/>
-      <c r="M4" s="227"/>
+      <c r="I4" s="179"/>
+      <c r="J4" s="175"/>
+      <c r="K4" s="176"/>
+      <c r="L4" s="176"/>
+      <c r="M4" s="177"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="298"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="214"/>
-      <c r="D5" s="214"/>
+      <c r="A5" s="284"/>
+      <c r="B5" s="196"/>
+      <c r="C5" s="196"/>
+      <c r="D5" s="196"/>
       <c r="E5" s="10">
         <v>61</v>
       </c>
-      <c r="F5" s="369">
+      <c r="F5" s="285">
         <v>61</v>
       </c>
-      <c r="G5" s="371"/>
+      <c r="G5" s="286"/>
       <c r="H5" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J5" s="202"/>
-      <c r="K5" s="202"/>
-      <c r="L5" s="202"/>
-      <c r="M5" s="217"/>
+      <c r="J5" s="199"/>
+      <c r="K5" s="199"/>
+      <c r="L5" s="199"/>
+      <c r="M5" s="200"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="298"/>
-      <c r="B6" s="214"/>
-      <c r="C6" s="214"/>
-      <c r="D6" s="214"/>
+      <c r="A6" s="284"/>
+      <c r="B6" s="196"/>
+      <c r="C6" s="196"/>
+      <c r="D6" s="196"/>
       <c r="E6" s="10">
         <v>83</v>
       </c>
-      <c r="F6" s="369">
+      <c r="F6" s="285">
         <v>83</v>
       </c>
-      <c r="G6" s="371"/>
+      <c r="G6" s="286"/>
       <c r="H6" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I6" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J6" s="202"/>
-      <c r="K6" s="202"/>
-      <c r="L6" s="202"/>
-      <c r="M6" s="217"/>
+      <c r="J6" s="199"/>
+      <c r="K6" s="199"/>
+      <c r="L6" s="199"/>
+      <c r="M6" s="200"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="298"/>
-      <c r="B7" s="214"/>
-      <c r="C7" s="214"/>
-      <c r="D7" s="214"/>
+      <c r="A7" s="284"/>
+      <c r="B7" s="196"/>
+      <c r="C7" s="196"/>
+      <c r="D7" s="196"/>
       <c r="E7" s="10">
         <v>70</v>
       </c>
-      <c r="F7" s="369">
+      <c r="F7" s="285">
         <v>70</v>
       </c>
-      <c r="G7" s="371"/>
+      <c r="G7" s="286"/>
       <c r="H7" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I7" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J7" s="202"/>
-      <c r="K7" s="202"/>
-      <c r="L7" s="202"/>
-      <c r="M7" s="217"/>
+      <c r="J7" s="199"/>
+      <c r="K7" s="199"/>
+      <c r="L7" s="199"/>
+      <c r="M7" s="200"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="298"/>
-      <c r="B8" s="214"/>
-      <c r="C8" s="214"/>
-      <c r="D8" s="214"/>
+      <c r="A8" s="284"/>
+      <c r="B8" s="196"/>
+      <c r="C8" s="196"/>
+      <c r="D8" s="196"/>
       <c r="E8" s="10">
         <v>50</v>
       </c>
-      <c r="F8" s="369">
+      <c r="F8" s="285">
         <v>50</v>
       </c>
-      <c r="G8" s="371"/>
+      <c r="G8" s="286"/>
       <c r="H8" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I8" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="202"/>
-      <c r="K8" s="202"/>
-      <c r="L8" s="202"/>
-      <c r="M8" s="217"/>
+      <c r="J8" s="199"/>
+      <c r="K8" s="199"/>
+      <c r="L8" s="199"/>
+      <c r="M8" s="200"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="298"/>
-      <c r="B9" s="214"/>
-      <c r="C9" s="214"/>
-      <c r="D9" s="214"/>
+      <c r="A9" s="284"/>
+      <c r="B9" s="196"/>
+      <c r="C9" s="196"/>
+      <c r="D9" s="196"/>
       <c r="E9" s="10">
         <v>70</v>
       </c>
-      <c r="F9" s="369">
+      <c r="F9" s="285">
         <v>70</v>
       </c>
-      <c r="G9" s="371"/>
+      <c r="G9" s="286"/>
       <c r="H9" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J9" s="202"/>
-      <c r="K9" s="202"/>
-      <c r="L9" s="202"/>
-      <c r="M9" s="217"/>
+      <c r="J9" s="199"/>
+      <c r="K9" s="199"/>
+      <c r="L9" s="199"/>
+      <c r="M9" s="200"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="298"/>
-      <c r="B10" s="214"/>
-      <c r="C10" s="214"/>
-      <c r="D10" s="214"/>
+      <c r="A10" s="284"/>
+      <c r="B10" s="196"/>
+      <c r="C10" s="196"/>
+      <c r="D10" s="196"/>
       <c r="E10" s="10">
         <v>69</v>
       </c>
-      <c r="F10" s="369">
+      <c r="F10" s="285">
         <v>69</v>
       </c>
-      <c r="G10" s="371"/>
+      <c r="G10" s="286"/>
       <c r="H10" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="202"/>
-      <c r="K10" s="202"/>
-      <c r="L10" s="202"/>
-      <c r="M10" s="217"/>
+      <c r="J10" s="199"/>
+      <c r="K10" s="199"/>
+      <c r="L10" s="199"/>
+      <c r="M10" s="200"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="298"/>
-      <c r="B11" s="214"/>
-      <c r="C11" s="214"/>
-      <c r="D11" s="214"/>
+      <c r="A11" s="284"/>
+      <c r="B11" s="196"/>
+      <c r="C11" s="196"/>
+      <c r="D11" s="196"/>
       <c r="E11" s="10">
         <v>54</v>
       </c>
-      <c r="F11" s="369">
+      <c r="F11" s="285">
         <v>54</v>
       </c>
-      <c r="G11" s="371"/>
+      <c r="G11" s="286"/>
       <c r="H11" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="202"/>
-      <c r="K11" s="202"/>
-      <c r="L11" s="202"/>
-      <c r="M11" s="217"/>
+      <c r="J11" s="199"/>
+      <c r="K11" s="199"/>
+      <c r="L11" s="199"/>
+      <c r="M11" s="200"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="298"/>
-      <c r="B12" s="214"/>
-      <c r="C12" s="214"/>
-      <c r="D12" s="214"/>
+      <c r="A12" s="284"/>
+      <c r="B12" s="196"/>
+      <c r="C12" s="196"/>
+      <c r="D12" s="196"/>
       <c r="E12" s="10">
         <v>65</v>
       </c>
-      <c r="F12" s="369">
+      <c r="F12" s="285">
         <v>65</v>
       </c>
-      <c r="G12" s="371"/>
+      <c r="G12" s="286"/>
       <c r="H12" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J12" s="202"/>
-      <c r="K12" s="202"/>
-      <c r="L12" s="202"/>
-      <c r="M12" s="217"/>
+      <c r="J12" s="199"/>
+      <c r="K12" s="199"/>
+      <c r="L12" s="199"/>
+      <c r="M12" s="200"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="298"/>
-      <c r="B13" s="214"/>
-      <c r="C13" s="214"/>
-      <c r="D13" s="214"/>
+      <c r="A13" s="284"/>
+      <c r="B13" s="196"/>
+      <c r="C13" s="196"/>
+      <c r="D13" s="196"/>
       <c r="E13" s="10">
         <v>65</v>
       </c>
-      <c r="F13" s="369">
+      <c r="F13" s="285">
         <v>65</v>
       </c>
-      <c r="G13" s="371"/>
+      <c r="G13" s="286"/>
       <c r="H13" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J13" s="202"/>
-      <c r="K13" s="202"/>
-      <c r="L13" s="202"/>
-      <c r="M13" s="217"/>
+      <c r="J13" s="199"/>
+      <c r="K13" s="199"/>
+      <c r="L13" s="199"/>
+      <c r="M13" s="200"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="298"/>
-      <c r="B14" s="214"/>
-      <c r="C14" s="214"/>
-      <c r="D14" s="214"/>
+      <c r="A14" s="284"/>
+      <c r="B14" s="196"/>
+      <c r="C14" s="196"/>
+      <c r="D14" s="196"/>
       <c r="E14" s="10">
         <v>70</v>
       </c>
-      <c r="F14" s="369">
+      <c r="F14" s="285">
         <v>70</v>
       </c>
-      <c r="G14" s="371"/>
+      <c r="G14" s="286"/>
       <c r="H14" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I14" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J14" s="202"/>
-      <c r="K14" s="202"/>
-      <c r="L14" s="202"/>
-      <c r="M14" s="217"/>
+      <c r="J14" s="199"/>
+      <c r="K14" s="199"/>
+      <c r="L14" s="199"/>
+      <c r="M14" s="200"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="298"/>
-      <c r="B15" s="214"/>
-      <c r="C15" s="214"/>
-      <c r="D15" s="214"/>
+      <c r="A15" s="284"/>
+      <c r="B15" s="196"/>
+      <c r="C15" s="196"/>
+      <c r="D15" s="196"/>
       <c r="E15" s="10">
         <v>55</v>
       </c>
-      <c r="F15" s="369">
+      <c r="F15" s="285">
         <v>55</v>
       </c>
-      <c r="G15" s="371"/>
+      <c r="G15" s="286"/>
       <c r="H15" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I15" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J15" s="202"/>
-      <c r="K15" s="202"/>
-      <c r="L15" s="202"/>
-      <c r="M15" s="217"/>
+      <c r="J15" s="199"/>
+      <c r="K15" s="199"/>
+      <c r="L15" s="199"/>
+      <c r="M15" s="200"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="298"/>
-      <c r="B16" s="214"/>
-      <c r="C16" s="214"/>
-      <c r="D16" s="214"/>
+      <c r="A16" s="284"/>
+      <c r="B16" s="196"/>
+      <c r="C16" s="196"/>
+      <c r="D16" s="196"/>
       <c r="E16" s="10">
         <v>54</v>
       </c>
-      <c r="F16" s="369">
+      <c r="F16" s="285">
         <v>54</v>
       </c>
-      <c r="G16" s="371"/>
+      <c r="G16" s="286"/>
       <c r="H16" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I16" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J16" s="202"/>
-      <c r="K16" s="202"/>
-      <c r="L16" s="202"/>
-      <c r="M16" s="217"/>
+      <c r="J16" s="199"/>
+      <c r="K16" s="199"/>
+      <c r="L16" s="199"/>
+      <c r="M16" s="200"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="298"/>
-      <c r="B17" s="214"/>
-      <c r="C17" s="214"/>
-      <c r="D17" s="214"/>
+      <c r="A17" s="284"/>
+      <c r="B17" s="196"/>
+      <c r="C17" s="196"/>
+      <c r="D17" s="196"/>
       <c r="E17" s="10">
         <v>76</v>
       </c>
-      <c r="F17" s="369">
+      <c r="F17" s="285">
         <v>76</v>
       </c>
-      <c r="G17" s="371"/>
+      <c r="G17" s="286"/>
       <c r="H17" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I17" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J17" s="202"/>
-      <c r="K17" s="202"/>
-      <c r="L17" s="202"/>
-      <c r="M17" s="217"/>
+      <c r="J17" s="199"/>
+      <c r="K17" s="199"/>
+      <c r="L17" s="199"/>
+      <c r="M17" s="200"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="298"/>
-      <c r="B18" s="214"/>
-      <c r="C18" s="214"/>
-      <c r="D18" s="214"/>
+      <c r="A18" s="284"/>
+      <c r="B18" s="196"/>
+      <c r="C18" s="196"/>
+      <c r="D18" s="196"/>
       <c r="E18" s="10">
         <v>76</v>
       </c>
-      <c r="F18" s="369">
+      <c r="F18" s="285">
         <v>76</v>
       </c>
-      <c r="G18" s="371"/>
+      <c r="G18" s="286"/>
       <c r="H18" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I18" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J18" s="202"/>
-      <c r="K18" s="202"/>
-      <c r="L18" s="202"/>
-      <c r="M18" s="217"/>
+      <c r="J18" s="199"/>
+      <c r="K18" s="199"/>
+      <c r="L18" s="199"/>
+      <c r="M18" s="200"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="298"/>
-      <c r="B19" s="214"/>
-      <c r="C19" s="214"/>
-      <c r="D19" s="214"/>
+      <c r="A19" s="284"/>
+      <c r="B19" s="196"/>
+      <c r="C19" s="196"/>
+      <c r="D19" s="196"/>
       <c r="E19" s="10">
         <v>65</v>
       </c>
-      <c r="F19" s="369">
+      <c r="F19" s="285">
         <v>65</v>
       </c>
-      <c r="G19" s="371"/>
+      <c r="G19" s="286"/>
       <c r="H19" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I19" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J19" s="202"/>
-      <c r="K19" s="202"/>
-      <c r="L19" s="202"/>
-      <c r="M19" s="217"/>
+      <c r="J19" s="199"/>
+      <c r="K19" s="199"/>
+      <c r="L19" s="199"/>
+      <c r="M19" s="200"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="298"/>
-      <c r="B20" s="214"/>
-      <c r="C20" s="214"/>
-      <c r="D20" s="214"/>
+      <c r="A20" s="284"/>
+      <c r="B20" s="196"/>
+      <c r="C20" s="196"/>
+      <c r="D20" s="196"/>
       <c r="E20" s="10">
         <v>56</v>
       </c>
-      <c r="F20" s="369">
+      <c r="F20" s="285">
         <v>56</v>
       </c>
-      <c r="G20" s="371"/>
+      <c r="G20" s="286"/>
       <c r="H20" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I20" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J20" s="202"/>
-      <c r="K20" s="202"/>
-      <c r="L20" s="202"/>
-      <c r="M20" s="217"/>
+      <c r="J20" s="199"/>
+      <c r="K20" s="199"/>
+      <c r="L20" s="199"/>
+      <c r="M20" s="200"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="298"/>
-      <c r="B21" s="214"/>
-      <c r="C21" s="214"/>
-      <c r="D21" s="214"/>
+      <c r="A21" s="284"/>
+      <c r="B21" s="196"/>
+      <c r="C21" s="196"/>
+      <c r="D21" s="196"/>
       <c r="E21" s="10">
         <v>83</v>
       </c>
-      <c r="F21" s="369">
+      <c r="F21" s="285">
         <v>83</v>
       </c>
-      <c r="G21" s="371"/>
+      <c r="G21" s="286"/>
       <c r="H21" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J21" s="202"/>
-      <c r="K21" s="202"/>
-      <c r="L21" s="202"/>
-      <c r="M21" s="217"/>
+      <c r="J21" s="199"/>
+      <c r="K21" s="199"/>
+      <c r="L21" s="199"/>
+      <c r="M21" s="200"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="298"/>
-      <c r="B22" s="214"/>
-      <c r="C22" s="214"/>
-      <c r="D22" s="214"/>
+      <c r="A22" s="284"/>
+      <c r="B22" s="196"/>
+      <c r="C22" s="196"/>
+      <c r="D22" s="196"/>
       <c r="E22" s="10">
         <v>27</v>
       </c>
-      <c r="F22" s="369">
+      <c r="F22" s="285">
         <v>27</v>
       </c>
-      <c r="G22" s="371"/>
+      <c r="G22" s="286"/>
       <c r="H22" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="202"/>
-      <c r="K22" s="202"/>
-      <c r="L22" s="202"/>
-      <c r="M22" s="217"/>
+      <c r="J22" s="199"/>
+      <c r="K22" s="199"/>
+      <c r="L22" s="199"/>
+      <c r="M22" s="200"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="298"/>
-      <c r="B23" s="214"/>
-      <c r="C23" s="214"/>
-      <c r="D23" s="214"/>
+      <c r="A23" s="284"/>
+      <c r="B23" s="196"/>
+      <c r="C23" s="196"/>
+      <c r="D23" s="196"/>
       <c r="E23" s="10">
         <v>16</v>
       </c>
-      <c r="F23" s="369">
+      <c r="F23" s="285">
         <v>16</v>
       </c>
-      <c r="G23" s="371"/>
+      <c r="G23" s="286"/>
       <c r="H23" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="202"/>
-      <c r="K23" s="202"/>
-      <c r="L23" s="202"/>
-      <c r="M23" s="217"/>
+      <c r="J23" s="199"/>
+      <c r="K23" s="199"/>
+      <c r="L23" s="199"/>
+      <c r="M23" s="200"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="298"/>
-      <c r="B24" s="214"/>
-      <c r="C24" s="214"/>
-      <c r="D24" s="214"/>
+      <c r="A24" s="284"/>
+      <c r="B24" s="196"/>
+      <c r="C24" s="196"/>
+      <c r="D24" s="196"/>
       <c r="E24" s="10">
         <v>26</v>
       </c>
-      <c r="F24" s="369">
+      <c r="F24" s="285">
         <v>26</v>
       </c>
-      <c r="G24" s="371"/>
+      <c r="G24" s="286"/>
       <c r="H24" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I24" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="202"/>
-      <c r="K24" s="202"/>
-      <c r="L24" s="202"/>
-      <c r="M24" s="217"/>
+      <c r="J24" s="199"/>
+      <c r="K24" s="199"/>
+      <c r="L24" s="199"/>
+      <c r="M24" s="200"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="298"/>
-      <c r="B25" s="214"/>
-      <c r="C25" s="214"/>
-      <c r="D25" s="214"/>
+      <c r="A25" s="284"/>
+      <c r="B25" s="196"/>
+      <c r="C25" s="196"/>
+      <c r="D25" s="196"/>
       <c r="E25" s="10">
         <v>16</v>
       </c>
-      <c r="F25" s="369">
+      <c r="F25" s="285">
         <v>16</v>
       </c>
-      <c r="G25" s="371"/>
+      <c r="G25" s="286"/>
       <c r="H25" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I25" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="202"/>
-      <c r="K25" s="202"/>
-      <c r="L25" s="202"/>
-      <c r="M25" s="217"/>
+      <c r="J25" s="199"/>
+      <c r="K25" s="199"/>
+      <c r="L25" s="199"/>
+      <c r="M25" s="200"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="293"/>
-      <c r="B26" s="294"/>
-      <c r="C26" s="294"/>
-      <c r="D26" s="294"/>
+      <c r="A26" s="287"/>
+      <c r="B26" s="288"/>
+      <c r="C26" s="288"/>
+      <c r="D26" s="288"/>
       <c r="E26" s="15"/>
-      <c r="F26" s="202"/>
-      <c r="G26" s="202"/>
+      <c r="F26" s="199"/>
+      <c r="G26" s="199"/>
       <c r="H26" s="15"/>
       <c r="I26" s="15"/>
-      <c r="J26" s="202"/>
-      <c r="K26" s="202"/>
-      <c r="L26" s="202"/>
-      <c r="M26" s="217"/>
+      <c r="J26" s="199"/>
+      <c r="K26" s="199"/>
+      <c r="L26" s="199"/>
+      <c r="M26" s="200"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="293"/>
-      <c r="B27" s="294"/>
-      <c r="C27" s="294"/>
-      <c r="D27" s="294"/>
+      <c r="A27" s="287"/>
+      <c r="B27" s="288"/>
+      <c r="C27" s="288"/>
+      <c r="D27" s="288"/>
       <c r="E27" s="15"/>
-      <c r="F27" s="202"/>
-      <c r="G27" s="202"/>
+      <c r="F27" s="199"/>
+      <c r="G27" s="199"/>
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
-      <c r="J27" s="202"/>
-      <c r="K27" s="202"/>
-      <c r="L27" s="202"/>
-      <c r="M27" s="217"/>
+      <c r="J27" s="199"/>
+      <c r="K27" s="199"/>
+      <c r="L27" s="199"/>
+      <c r="M27" s="200"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="293"/>
-      <c r="B28" s="294"/>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
+      <c r="A28" s="287"/>
+      <c r="B28" s="288"/>
+      <c r="C28" s="288"/>
+      <c r="D28" s="288"/>
       <c r="E28" s="15"/>
-      <c r="F28" s="202"/>
-      <c r="G28" s="202"/>
+      <c r="F28" s="199"/>
+      <c r="G28" s="199"/>
       <c r="H28" s="15"/>
       <c r="I28" s="15"/>
-      <c r="J28" s="202"/>
-      <c r="K28" s="202"/>
-      <c r="L28" s="202"/>
-      <c r="M28" s="217"/>
+      <c r="J28" s="199"/>
+      <c r="K28" s="199"/>
+      <c r="L28" s="199"/>
+      <c r="M28" s="200"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="293"/>
-      <c r="B29" s="294"/>
-      <c r="C29" s="294"/>
-      <c r="D29" s="294"/>
+      <c r="A29" s="287"/>
+      <c r="B29" s="288"/>
+      <c r="C29" s="288"/>
+      <c r="D29" s="288"/>
       <c r="E29" s="15"/>
-      <c r="F29" s="202"/>
-      <c r="G29" s="202"/>
+      <c r="F29" s="199"/>
+      <c r="G29" s="199"/>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
-      <c r="J29" s="202"/>
-      <c r="K29" s="202"/>
-      <c r="L29" s="202"/>
-      <c r="M29" s="217"/>
+      <c r="J29" s="199"/>
+      <c r="K29" s="199"/>
+      <c r="L29" s="199"/>
+      <c r="M29" s="200"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="293"/>
-      <c r="B30" s="294"/>
-      <c r="C30" s="294"/>
-      <c r="D30" s="294"/>
+      <c r="A30" s="287"/>
+      <c r="B30" s="288"/>
+      <c r="C30" s="288"/>
+      <c r="D30" s="288"/>
       <c r="E30" s="15"/>
-      <c r="F30" s="202"/>
-      <c r="G30" s="202"/>
+      <c r="F30" s="199"/>
+      <c r="G30" s="199"/>
       <c r="H30" s="15"/>
       <c r="I30" s="15"/>
-      <c r="J30" s="202"/>
-      <c r="K30" s="202"/>
-      <c r="L30" s="202"/>
-      <c r="M30" s="217"/>
+      <c r="J30" s="199"/>
+      <c r="K30" s="199"/>
+      <c r="L30" s="199"/>
+      <c r="M30" s="200"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="293"/>
-      <c r="B31" s="294"/>
-      <c r="C31" s="294"/>
-      <c r="D31" s="294"/>
+      <c r="A31" s="287"/>
+      <c r="B31" s="288"/>
+      <c r="C31" s="288"/>
+      <c r="D31" s="288"/>
       <c r="E31" s="15"/>
-      <c r="F31" s="202"/>
-      <c r="G31" s="202"/>
+      <c r="F31" s="199"/>
+      <c r="G31" s="199"/>
       <c r="H31" s="15"/>
       <c r="I31" s="15"/>
-      <c r="J31" s="202"/>
-      <c r="K31" s="202"/>
-      <c r="L31" s="202"/>
-      <c r="M31" s="217"/>
+      <c r="J31" s="199"/>
+      <c r="K31" s="199"/>
+      <c r="L31" s="199"/>
+      <c r="M31" s="200"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="293"/>
-      <c r="B32" s="294"/>
-      <c r="C32" s="294"/>
-      <c r="D32" s="294"/>
+      <c r="A32" s="287"/>
+      <c r="B32" s="288"/>
+      <c r="C32" s="288"/>
+      <c r="D32" s="288"/>
       <c r="E32" s="15"/>
-      <c r="F32" s="202"/>
-      <c r="G32" s="202"/>
+      <c r="F32" s="199"/>
+      <c r="G32" s="199"/>
       <c r="H32" s="15"/>
       <c r="I32" s="15"/>
-      <c r="J32" s="202"/>
-      <c r="K32" s="202"/>
-      <c r="L32" s="202"/>
-      <c r="M32" s="217"/>
+      <c r="J32" s="199"/>
+      <c r="K32" s="199"/>
+      <c r="L32" s="199"/>
+      <c r="M32" s="200"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A33" s="293"/>
-      <c r="B33" s="294"/>
-      <c r="C33" s="294"/>
-      <c r="D33" s="294"/>
+      <c r="A33" s="287"/>
+      <c r="B33" s="288"/>
+      <c r="C33" s="288"/>
+      <c r="D33" s="288"/>
       <c r="E33" s="15"/>
-      <c r="F33" s="202"/>
-      <c r="G33" s="202"/>
+      <c r="F33" s="199"/>
+      <c r="G33" s="199"/>
       <c r="H33" s="15"/>
       <c r="I33" s="15"/>
-      <c r="J33" s="202"/>
-      <c r="K33" s="202"/>
-      <c r="L33" s="202"/>
-      <c r="M33" s="217"/>
+      <c r="J33" s="199"/>
+      <c r="K33" s="199"/>
+      <c r="L33" s="199"/>
+      <c r="M33" s="200"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34" s="293"/>
-      <c r="B34" s="294"/>
-      <c r="C34" s="294"/>
-      <c r="D34" s="294"/>
+      <c r="A34" s="287"/>
+      <c r="B34" s="288"/>
+      <c r="C34" s="288"/>
+      <c r="D34" s="288"/>
       <c r="E34" s="15"/>
-      <c r="F34" s="202"/>
-      <c r="G34" s="202"/>
+      <c r="F34" s="199"/>
+      <c r="G34" s="199"/>
       <c r="H34" s="15"/>
       <c r="I34" s="15"/>
-      <c r="J34" s="202"/>
-      <c r="K34" s="202"/>
-      <c r="L34" s="202"/>
-      <c r="M34" s="217"/>
+      <c r="J34" s="199"/>
+      <c r="K34" s="199"/>
+      <c r="L34" s="199"/>
+      <c r="M34" s="200"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="293"/>
-      <c r="B35" s="294"/>
-      <c r="C35" s="294"/>
-      <c r="D35" s="294"/>
+      <c r="A35" s="287"/>
+      <c r="B35" s="288"/>
+      <c r="C35" s="288"/>
+      <c r="D35" s="288"/>
       <c r="E35" s="15"/>
-      <c r="F35" s="202"/>
-      <c r="G35" s="202"/>
+      <c r="F35" s="199"/>
+      <c r="G35" s="199"/>
       <c r="H35" s="15"/>
       <c r="I35" s="15"/>
-      <c r="J35" s="202"/>
-      <c r="K35" s="202"/>
-      <c r="L35" s="202"/>
-      <c r="M35" s="217"/>
+      <c r="J35" s="199"/>
+      <c r="K35" s="199"/>
+      <c r="L35" s="199"/>
+      <c r="M35" s="200"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" s="293"/>
-      <c r="B36" s="294"/>
-      <c r="C36" s="294"/>
-      <c r="D36" s="294"/>
+      <c r="A36" s="287"/>
+      <c r="B36" s="288"/>
+      <c r="C36" s="288"/>
+      <c r="D36" s="288"/>
       <c r="E36" s="15"/>
-      <c r="F36" s="202"/>
-      <c r="G36" s="202"/>
+      <c r="F36" s="199"/>
+      <c r="G36" s="199"/>
       <c r="H36" s="15"/>
       <c r="I36" s="15"/>
-      <c r="J36" s="202"/>
-      <c r="K36" s="202"/>
-      <c r="L36" s="202"/>
-      <c r="M36" s="217"/>
+      <c r="J36" s="199"/>
+      <c r="K36" s="199"/>
+      <c r="L36" s="199"/>
+      <c r="M36" s="200"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="293"/>
-      <c r="B37" s="294"/>
-      <c r="C37" s="294"/>
-      <c r="D37" s="294"/>
+      <c r="A37" s="287"/>
+      <c r="B37" s="288"/>
+      <c r="C37" s="288"/>
+      <c r="D37" s="288"/>
       <c r="E37" s="15"/>
-      <c r="F37" s="202"/>
-      <c r="G37" s="202"/>
+      <c r="F37" s="199"/>
+      <c r="G37" s="199"/>
       <c r="H37" s="15"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="202"/>
-      <c r="K37" s="202"/>
-      <c r="L37" s="202"/>
-      <c r="M37" s="217"/>
+      <c r="J37" s="199"/>
+      <c r="K37" s="199"/>
+      <c r="L37" s="199"/>
+      <c r="M37" s="200"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A38" s="293"/>
-      <c r="B38" s="294"/>
-      <c r="C38" s="294"/>
-      <c r="D38" s="294"/>
+      <c r="A38" s="287"/>
+      <c r="B38" s="288"/>
+      <c r="C38" s="288"/>
+      <c r="D38" s="288"/>
       <c r="E38" s="15"/>
-      <c r="F38" s="202"/>
-      <c r="G38" s="202"/>
+      <c r="F38" s="199"/>
+      <c r="G38" s="199"/>
       <c r="H38" s="15"/>
       <c r="I38" s="15"/>
-      <c r="J38" s="202"/>
-      <c r="K38" s="202"/>
-      <c r="L38" s="202"/>
-      <c r="M38" s="217"/>
+      <c r="J38" s="199"/>
+      <c r="K38" s="199"/>
+      <c r="L38" s="199"/>
+      <c r="M38" s="200"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A39" s="293"/>
-      <c r="B39" s="294"/>
-      <c r="C39" s="294"/>
-      <c r="D39" s="294"/>
+      <c r="A39" s="287"/>
+      <c r="B39" s="288"/>
+      <c r="C39" s="288"/>
+      <c r="D39" s="288"/>
       <c r="E39" s="15"/>
-      <c r="F39" s="202"/>
-      <c r="G39" s="202"/>
+      <c r="F39" s="199"/>
+      <c r="G39" s="199"/>
       <c r="H39" s="15"/>
       <c r="I39" s="15"/>
-      <c r="J39" s="202"/>
-      <c r="K39" s="202"/>
-      <c r="L39" s="202"/>
-      <c r="M39" s="217"/>
+      <c r="J39" s="199"/>
+      <c r="K39" s="199"/>
+      <c r="L39" s="199"/>
+      <c r="M39" s="200"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A40" s="293"/>
-      <c r="B40" s="294"/>
-      <c r="C40" s="294"/>
-      <c r="D40" s="294"/>
+      <c r="A40" s="287"/>
+      <c r="B40" s="288"/>
+      <c r="C40" s="288"/>
+      <c r="D40" s="288"/>
       <c r="E40" s="15"/>
-      <c r="F40" s="202"/>
-      <c r="G40" s="202"/>
+      <c r="F40" s="199"/>
+      <c r="G40" s="199"/>
       <c r="H40" s="15"/>
       <c r="I40" s="15"/>
-      <c r="J40" s="202"/>
-      <c r="K40" s="202"/>
-      <c r="L40" s="202"/>
-      <c r="M40" s="217"/>
+      <c r="J40" s="199"/>
+      <c r="K40" s="199"/>
+      <c r="L40" s="199"/>
+      <c r="M40" s="200"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A41" s="293"/>
-      <c r="B41" s="294"/>
-      <c r="C41" s="294"/>
-      <c r="D41" s="294"/>
+      <c r="A41" s="287"/>
+      <c r="B41" s="288"/>
+      <c r="C41" s="288"/>
+      <c r="D41" s="288"/>
       <c r="E41" s="15"/>
-      <c r="F41" s="202"/>
-      <c r="G41" s="202"/>
+      <c r="F41" s="199"/>
+      <c r="G41" s="199"/>
       <c r="H41" s="15"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="202"/>
-      <c r="K41" s="202"/>
-      <c r="L41" s="202"/>
-      <c r="M41" s="217"/>
+      <c r="J41" s="199"/>
+      <c r="K41" s="199"/>
+      <c r="L41" s="199"/>
+      <c r="M41" s="200"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A42" s="293"/>
-      <c r="B42" s="294"/>
-      <c r="C42" s="294"/>
-      <c r="D42" s="294"/>
+      <c r="A42" s="287"/>
+      <c r="B42" s="288"/>
+      <c r="C42" s="288"/>
+      <c r="D42" s="288"/>
       <c r="E42" s="15"/>
-      <c r="F42" s="202"/>
-      <c r="G42" s="202"/>
+      <c r="F42" s="199"/>
+      <c r="G42" s="199"/>
       <c r="H42" s="15"/>
       <c r="I42" s="15"/>
-      <c r="J42" s="202"/>
-      <c r="K42" s="202"/>
-      <c r="L42" s="202"/>
-      <c r="M42" s="217"/>
+      <c r="J42" s="199"/>
+      <c r="K42" s="199"/>
+      <c r="L42" s="199"/>
+      <c r="M42" s="200"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A43" s="293"/>
-      <c r="B43" s="294"/>
-      <c r="C43" s="294"/>
-      <c r="D43" s="294"/>
+      <c r="A43" s="287"/>
+      <c r="B43" s="288"/>
+      <c r="C43" s="288"/>
+      <c r="D43" s="288"/>
       <c r="E43" s="15"/>
-      <c r="F43" s="202"/>
-      <c r="G43" s="202"/>
+      <c r="F43" s="199"/>
+      <c r="G43" s="199"/>
       <c r="H43" s="15"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="202"/>
-      <c r="K43" s="202"/>
-      <c r="L43" s="202"/>
-      <c r="M43" s="217"/>
+      <c r="J43" s="199"/>
+      <c r="K43" s="199"/>
+      <c r="L43" s="199"/>
+      <c r="M43" s="200"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A44" s="293"/>
-      <c r="B44" s="294"/>
-      <c r="C44" s="294"/>
-      <c r="D44" s="294"/>
+      <c r="A44" s="287"/>
+      <c r="B44" s="288"/>
+      <c r="C44" s="288"/>
+      <c r="D44" s="288"/>
       <c r="E44" s="15"/>
-      <c r="F44" s="202"/>
-      <c r="G44" s="202"/>
+      <c r="F44" s="199"/>
+      <c r="G44" s="199"/>
       <c r="H44" s="15"/>
       <c r="I44" s="15"/>
-      <c r="J44" s="202"/>
-      <c r="K44" s="202"/>
-      <c r="L44" s="202"/>
-      <c r="M44" s="217"/>
+      <c r="J44" s="199"/>
+      <c r="K44" s="199"/>
+      <c r="L44" s="199"/>
+      <c r="M44" s="200"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A45" s="293"/>
-      <c r="B45" s="294"/>
-      <c r="C45" s="294"/>
-      <c r="D45" s="294"/>
+      <c r="A45" s="287"/>
+      <c r="B45" s="288"/>
+      <c r="C45" s="288"/>
+      <c r="D45" s="288"/>
       <c r="E45" s="15"/>
-      <c r="F45" s="202"/>
-      <c r="G45" s="202"/>
+      <c r="F45" s="199"/>
+      <c r="G45" s="199"/>
       <c r="H45" s="15"/>
       <c r="I45" s="15"/>
-      <c r="J45" s="202"/>
-      <c r="K45" s="202"/>
-      <c r="L45" s="202"/>
-      <c r="M45" s="217"/>
+      <c r="J45" s="199"/>
+      <c r="K45" s="199"/>
+      <c r="L45" s="199"/>
+      <c r="M45" s="200"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A46" s="293"/>
-      <c r="B46" s="294"/>
-      <c r="C46" s="294"/>
-      <c r="D46" s="294"/>
+      <c r="A46" s="287"/>
+      <c r="B46" s="288"/>
+      <c r="C46" s="288"/>
+      <c r="D46" s="288"/>
       <c r="E46" s="15"/>
-      <c r="F46" s="202"/>
-      <c r="G46" s="202"/>
+      <c r="F46" s="199"/>
+      <c r="G46" s="199"/>
       <c r="H46" s="15"/>
       <c r="I46" s="15"/>
-      <c r="J46" s="202"/>
-      <c r="K46" s="202"/>
-      <c r="L46" s="202"/>
-      <c r="M46" s="217"/>
+      <c r="J46" s="199"/>
+      <c r="K46" s="199"/>
+      <c r="L46" s="199"/>
+      <c r="M46" s="200"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A47" s="293"/>
-      <c r="B47" s="294"/>
-      <c r="C47" s="294"/>
-      <c r="D47" s="294"/>
+      <c r="A47" s="287"/>
+      <c r="B47" s="288"/>
+      <c r="C47" s="288"/>
+      <c r="D47" s="288"/>
       <c r="E47" s="15"/>
-      <c r="F47" s="202"/>
-      <c r="G47" s="202"/>
+      <c r="F47" s="199"/>
+      <c r="G47" s="199"/>
       <c r="H47" s="15"/>
       <c r="I47" s="15"/>
-      <c r="J47" s="202"/>
-      <c r="K47" s="202"/>
-      <c r="L47" s="202"/>
-      <c r="M47" s="217"/>
+      <c r="J47" s="199"/>
+      <c r="K47" s="199"/>
+      <c r="L47" s="199"/>
+      <c r="M47" s="200"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" s="293"/>
-      <c r="B48" s="294"/>
-      <c r="C48" s="294"/>
-      <c r="D48" s="294"/>
+      <c r="A48" s="287"/>
+      <c r="B48" s="288"/>
+      <c r="C48" s="288"/>
+      <c r="D48" s="288"/>
       <c r="E48" s="15"/>
-      <c r="F48" s="202"/>
-      <c r="G48" s="202"/>
+      <c r="F48" s="199"/>
+      <c r="G48" s="199"/>
       <c r="H48" s="15"/>
       <c r="I48" s="15"/>
-      <c r="J48" s="202"/>
-      <c r="K48" s="202"/>
-      <c r="L48" s="202"/>
-      <c r="M48" s="217"/>
+      <c r="J48" s="199"/>
+      <c r="K48" s="199"/>
+      <c r="L48" s="199"/>
+      <c r="M48" s="200"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A49" s="293"/>
-      <c r="B49" s="294"/>
-      <c r="C49" s="294"/>
-      <c r="D49" s="294"/>
+      <c r="A49" s="287"/>
+      <c r="B49" s="288"/>
+      <c r="C49" s="288"/>
+      <c r="D49" s="288"/>
       <c r="E49" s="15"/>
-      <c r="F49" s="202"/>
-      <c r="G49" s="202"/>
+      <c r="F49" s="199"/>
+      <c r="G49" s="199"/>
       <c r="H49" s="15"/>
       <c r="I49" s="15"/>
-      <c r="J49" s="202"/>
-      <c r="K49" s="202"/>
-      <c r="L49" s="202"/>
-      <c r="M49" s="217"/>
+      <c r="J49" s="199"/>
+      <c r="K49" s="199"/>
+      <c r="L49" s="199"/>
+      <c r="M49" s="200"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="199" t="s">
+      <c r="A50" s="206" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="200"/>
-      <c r="C50" s="200"/>
-      <c r="D50" s="200"/>
+      <c r="B50" s="207"/>
+      <c r="C50" s="207"/>
+      <c r="D50" s="207"/>
       <c r="E50" s="23">
         <f>SUM(E5:E25,'Master BOL'!E22:E29)</f>
         <v>1688</v>
       </c>
-      <c r="F50" s="295">
+      <c r="F50" s="301">
         <f>SUM(F5:F25,'Master BOL'!F22:F29)</f>
         <v>1688</v>
       </c>
-      <c r="G50" s="216"/>
+      <c r="G50" s="302"/>
       <c r="H50" s="50"/>
       <c r="I50" s="51"/>
-      <c r="J50" s="296"/>
-      <c r="K50" s="296"/>
-      <c r="L50" s="296"/>
-      <c r="M50" s="297"/>
+      <c r="J50" s="303"/>
+      <c r="K50" s="303"/>
+      <c r="L50" s="303"/>
+      <c r="M50" s="304"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A51" s="281" t="s">
+      <c r="A51" s="289" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="282"/>
-      <c r="C51" s="282"/>
-      <c r="D51" s="282"/>
-      <c r="E51" s="282"/>
-      <c r="F51" s="282"/>
-      <c r="G51" s="282"/>
-      <c r="H51" s="282"/>
-      <c r="I51" s="282"/>
-      <c r="J51" s="282"/>
-      <c r="K51" s="282"/>
-      <c r="L51" s="282"/>
-      <c r="M51" s="283"/>
+      <c r="B51" s="290"/>
+      <c r="C51" s="290"/>
+      <c r="D51" s="290"/>
+      <c r="E51" s="290"/>
+      <c r="F51" s="290"/>
+      <c r="G51" s="290"/>
+      <c r="H51" s="290"/>
+      <c r="I51" s="290"/>
+      <c r="J51" s="290"/>
+      <c r="K51" s="290"/>
+      <c r="L51" s="290"/>
+      <c r="M51" s="291"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="284"/>
-      <c r="B52" s="285"/>
-      <c r="C52" s="285"/>
-      <c r="D52" s="285"/>
-      <c r="E52" s="285"/>
-      <c r="F52" s="285"/>
-      <c r="G52" s="285"/>
-      <c r="H52" s="285"/>
-      <c r="I52" s="285"/>
-      <c r="J52" s="285"/>
-      <c r="K52" s="285"/>
-      <c r="L52" s="285"/>
-      <c r="M52" s="286"/>
+      <c r="A52" s="292"/>
+      <c r="B52" s="293"/>
+      <c r="C52" s="293"/>
+      <c r="D52" s="293"/>
+      <c r="E52" s="293"/>
+      <c r="F52" s="293"/>
+      <c r="G52" s="293"/>
+      <c r="H52" s="293"/>
+      <c r="I52" s="293"/>
+      <c r="J52" s="293"/>
+      <c r="K52" s="293"/>
+      <c r="L52" s="293"/>
+      <c r="M52" s="294"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A53" s="287"/>
-      <c r="B53" s="288"/>
-      <c r="C53" s="288"/>
-      <c r="D53" s="288"/>
-      <c r="E53" s="288"/>
-      <c r="F53" s="288"/>
-      <c r="G53" s="288"/>
-      <c r="H53" s="288"/>
-      <c r="I53" s="288"/>
-      <c r="J53" s="288"/>
-      <c r="K53" s="288"/>
-      <c r="L53" s="288"/>
-      <c r="M53" s="289"/>
+      <c r="A53" s="295"/>
+      <c r="B53" s="296"/>
+      <c r="C53" s="296"/>
+      <c r="D53" s="296"/>
+      <c r="E53" s="296"/>
+      <c r="F53" s="296"/>
+      <c r="G53" s="296"/>
+      <c r="H53" s="296"/>
+      <c r="I53" s="296"/>
+      <c r="J53" s="296"/>
+      <c r="K53" s="296"/>
+      <c r="L53" s="296"/>
+      <c r="M53" s="297"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A54" s="287"/>
-      <c r="B54" s="288"/>
-      <c r="C54" s="288"/>
-      <c r="D54" s="288"/>
-      <c r="E54" s="288"/>
-      <c r="F54" s="288"/>
-      <c r="G54" s="288"/>
-      <c r="H54" s="288"/>
-      <c r="I54" s="288"/>
-      <c r="J54" s="288"/>
-      <c r="K54" s="288"/>
-      <c r="L54" s="288"/>
-      <c r="M54" s="289"/>
+      <c r="A54" s="295"/>
+      <c r="B54" s="296"/>
+      <c r="C54" s="296"/>
+      <c r="D54" s="296"/>
+      <c r="E54" s="296"/>
+      <c r="F54" s="296"/>
+      <c r="G54" s="296"/>
+      <c r="H54" s="296"/>
+      <c r="I54" s="296"/>
+      <c r="J54" s="296"/>
+      <c r="K54" s="296"/>
+      <c r="L54" s="296"/>
+      <c r="M54" s="297"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A55" s="287"/>
-      <c r="B55" s="288"/>
-      <c r="C55" s="288"/>
-      <c r="D55" s="288"/>
-      <c r="E55" s="288"/>
-      <c r="F55" s="288"/>
-      <c r="G55" s="288"/>
-      <c r="H55" s="288"/>
-      <c r="I55" s="288"/>
-      <c r="J55" s="288"/>
-      <c r="K55" s="288"/>
-      <c r="L55" s="288"/>
-      <c r="M55" s="289"/>
+      <c r="A55" s="295"/>
+      <c r="B55" s="296"/>
+      <c r="C55" s="296"/>
+      <c r="D55" s="296"/>
+      <c r="E55" s="296"/>
+      <c r="F55" s="296"/>
+      <c r="G55" s="296"/>
+      <c r="H55" s="296"/>
+      <c r="I55" s="296"/>
+      <c r="J55" s="296"/>
+      <c r="K55" s="296"/>
+      <c r="L55" s="296"/>
+      <c r="M55" s="297"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A56" s="287"/>
-      <c r="B56" s="288"/>
-      <c r="C56" s="288"/>
-      <c r="D56" s="288"/>
-      <c r="E56" s="288"/>
-      <c r="F56" s="288"/>
-      <c r="G56" s="288"/>
-      <c r="H56" s="288"/>
-      <c r="I56" s="288"/>
-      <c r="J56" s="288"/>
-      <c r="K56" s="288"/>
-      <c r="L56" s="288"/>
-      <c r="M56" s="289"/>
+      <c r="A56" s="295"/>
+      <c r="B56" s="296"/>
+      <c r="C56" s="296"/>
+      <c r="D56" s="296"/>
+      <c r="E56" s="296"/>
+      <c r="F56" s="296"/>
+      <c r="G56" s="296"/>
+      <c r="H56" s="296"/>
+      <c r="I56" s="296"/>
+      <c r="J56" s="296"/>
+      <c r="K56" s="296"/>
+      <c r="L56" s="296"/>
+      <c r="M56" s="297"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" s="287"/>
-      <c r="B57" s="288"/>
-      <c r="C57" s="288"/>
-      <c r="D57" s="288"/>
-      <c r="E57" s="288"/>
-      <c r="F57" s="288"/>
-      <c r="G57" s="288"/>
-      <c r="H57" s="288"/>
-      <c r="I57" s="288"/>
-      <c r="J57" s="288"/>
-      <c r="K57" s="288"/>
-      <c r="L57" s="288"/>
-      <c r="M57" s="289"/>
+      <c r="A57" s="295"/>
+      <c r="B57" s="296"/>
+      <c r="C57" s="296"/>
+      <c r="D57" s="296"/>
+      <c r="E57" s="296"/>
+      <c r="F57" s="296"/>
+      <c r="G57" s="296"/>
+      <c r="H57" s="296"/>
+      <c r="I57" s="296"/>
+      <c r="J57" s="296"/>
+      <c r="K57" s="296"/>
+      <c r="L57" s="296"/>
+      <c r="M57" s="297"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="287"/>
-      <c r="B58" s="288"/>
-      <c r="C58" s="288"/>
-      <c r="D58" s="288"/>
-      <c r="E58" s="288"/>
-      <c r="F58" s="288"/>
-      <c r="G58" s="288"/>
-      <c r="H58" s="288"/>
-      <c r="I58" s="288"/>
-      <c r="J58" s="288"/>
-      <c r="K58" s="288"/>
-      <c r="L58" s="288"/>
-      <c r="M58" s="289"/>
+      <c r="A58" s="295"/>
+      <c r="B58" s="296"/>
+      <c r="C58" s="296"/>
+      <c r="D58" s="296"/>
+      <c r="E58" s="296"/>
+      <c r="F58" s="296"/>
+      <c r="G58" s="296"/>
+      <c r="H58" s="296"/>
+      <c r="I58" s="296"/>
+      <c r="J58" s="296"/>
+      <c r="K58" s="296"/>
+      <c r="L58" s="296"/>
+      <c r="M58" s="297"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A59" s="287"/>
-      <c r="B59" s="288"/>
-      <c r="C59" s="288"/>
-      <c r="D59" s="288"/>
-      <c r="E59" s="288"/>
-      <c r="F59" s="288"/>
-      <c r="G59" s="288"/>
-      <c r="H59" s="288"/>
-      <c r="I59" s="288"/>
-      <c r="J59" s="288"/>
-      <c r="K59" s="288"/>
-      <c r="L59" s="288"/>
-      <c r="M59" s="289"/>
+      <c r="A59" s="295"/>
+      <c r="B59" s="296"/>
+      <c r="C59" s="296"/>
+      <c r="D59" s="296"/>
+      <c r="E59" s="296"/>
+      <c r="F59" s="296"/>
+      <c r="G59" s="296"/>
+      <c r="H59" s="296"/>
+      <c r="I59" s="296"/>
+      <c r="J59" s="296"/>
+      <c r="K59" s="296"/>
+      <c r="L59" s="296"/>
+      <c r="M59" s="297"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A60" s="290"/>
-      <c r="B60" s="291"/>
-      <c r="C60" s="291"/>
-      <c r="D60" s="291"/>
-      <c r="E60" s="291"/>
-      <c r="F60" s="291"/>
-      <c r="G60" s="291"/>
-      <c r="H60" s="291"/>
-      <c r="I60" s="291"/>
-      <c r="J60" s="291"/>
-      <c r="K60" s="291"/>
-      <c r="L60" s="291"/>
-      <c r="M60" s="292"/>
+      <c r="A60" s="298"/>
+      <c r="B60" s="299"/>
+      <c r="C60" s="299"/>
+      <c r="D60" s="299"/>
+      <c r="E60" s="299"/>
+      <c r="F60" s="299"/>
+      <c r="G60" s="299"/>
+      <c r="H60" s="299"/>
+      <c r="I60" s="299"/>
+      <c r="J60" s="299"/>
+      <c r="K60" s="299"/>
+      <c r="L60" s="299"/>
+      <c r="M60" s="300"/>
     </row>
     <row r="61" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="49"/>
@@ -8087,6 +8087,140 @@
     </row>
   </sheetData>
   <mergeCells count="150">
+    <mergeCell ref="A51:M51"/>
+    <mergeCell ref="A52:M60"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="J49:M49"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="J44:M44"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="J42:M42"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="J40:M40"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="J8:M8"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="J5:M5"/>
@@ -8103,140 +8237,6 @@
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="J3:M4"/>
     <mergeCell ref="H4:I4"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="J12:M12"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="J42:M42"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="J40:M40"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="J46:M46"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="J44:M44"/>
-    <mergeCell ref="A51:M51"/>
-    <mergeCell ref="A52:M60"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="J49:M49"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="J47:M47"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="J48:M48"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.26" top="0.2" bottom="0.27" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8263,10 +8263,10 @@
       <c r="A1" s="78" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="304">
+      <c r="B1" s="421">
         <v>45877</v>
       </c>
-      <c r="C1" s="304"/>
+      <c r="C1" s="421"/>
       <c r="F1" s="79"/>
       <c r="G1" s="79" t="s">
         <v>71</v>
@@ -8275,22 +8275,22 @@
       <c r="I1" s="79"/>
       <c r="J1" s="80"/>
       <c r="K1" s="80"/>
-      <c r="L1" s="311" t="s">
+      <c r="L1" s="426" t="s">
         <v>72</v>
       </c>
-      <c r="M1" s="312"/>
+      <c r="M1" s="427"/>
     </row>
     <row r="2" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="308" t="s">
+      <c r="A2" s="423" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="309"/>
-      <c r="C2" s="309"/>
-      <c r="D2" s="309"/>
-      <c r="E2" s="309"/>
-      <c r="F2" s="309"/>
-      <c r="G2" s="309"/>
-      <c r="H2" s="310"/>
+      <c r="B2" s="424"/>
+      <c r="C2" s="424"/>
+      <c r="D2" s="424"/>
+      <c r="E2" s="424"/>
+      <c r="F2" s="424"/>
+      <c r="G2" s="424"/>
+      <c r="H2" s="425"/>
       <c r="I2" s="81"/>
       <c r="J2" s="82"/>
       <c r="K2" s="82"/>
@@ -8298,16 +8298,16 @@
       <c r="M2" s="83"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="318" t="s">
+      <c r="A3" s="388" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="319"/>
-      <c r="C3" s="319"/>
-      <c r="D3" s="319"/>
-      <c r="E3" s="319"/>
-      <c r="F3" s="319"/>
-      <c r="G3" s="319"/>
-      <c r="H3" s="320"/>
+      <c r="B3" s="389"/>
+      <c r="C3" s="389"/>
+      <c r="D3" s="389"/>
+      <c r="E3" s="389"/>
+      <c r="F3" s="389"/>
+      <c r="G3" s="389"/>
+      <c r="H3" s="390"/>
       <c r="I3" s="84" t="s">
         <v>193</v>
       </c>
@@ -8317,69 +8317,69 @@
       <c r="M3" s="86"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="318" t="s">
+      <c r="A4" s="388" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="319"/>
-      <c r="C4" s="319"/>
-      <c r="D4" s="319"/>
-      <c r="E4" s="319"/>
-      <c r="F4" s="319"/>
-      <c r="G4" s="319"/>
-      <c r="H4" s="320"/>
-      <c r="I4" s="322"/>
-      <c r="J4" s="300"/>
-      <c r="K4" s="300"/>
-      <c r="L4" s="300"/>
-      <c r="M4" s="301"/>
+      <c r="B4" s="389"/>
+      <c r="C4" s="389"/>
+      <c r="D4" s="389"/>
+      <c r="E4" s="389"/>
+      <c r="F4" s="389"/>
+      <c r="G4" s="389"/>
+      <c r="H4" s="390"/>
+      <c r="I4" s="433"/>
+      <c r="J4" s="417"/>
+      <c r="K4" s="417"/>
+      <c r="L4" s="417"/>
+      <c r="M4" s="418"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="318" t="s">
+      <c r="A5" s="388" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="319"/>
-      <c r="C5" s="319"/>
-      <c r="D5" s="319"/>
-      <c r="E5" s="319"/>
-      <c r="F5" s="319"/>
-      <c r="G5" s="319"/>
-      <c r="H5" s="320"/>
-      <c r="I5" s="322"/>
-      <c r="J5" s="300"/>
-      <c r="K5" s="300"/>
-      <c r="L5" s="300"/>
-      <c r="M5" s="301"/>
+      <c r="B5" s="389"/>
+      <c r="C5" s="389"/>
+      <c r="D5" s="389"/>
+      <c r="E5" s="389"/>
+      <c r="F5" s="389"/>
+      <c r="G5" s="389"/>
+      <c r="H5" s="390"/>
+      <c r="I5" s="433"/>
+      <c r="J5" s="417"/>
+      <c r="K5" s="417"/>
+      <c r="L5" s="417"/>
+      <c r="M5" s="418"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="316" t="s">
+      <c r="A6" s="431" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="317"/>
-      <c r="C6" s="317"/>
-      <c r="D6" s="317"/>
-      <c r="E6" s="317"/>
-      <c r="F6" s="321" t="s">
+      <c r="B6" s="387"/>
+      <c r="C6" s="387"/>
+      <c r="D6" s="387"/>
+      <c r="E6" s="387"/>
+      <c r="F6" s="432" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="321"/>
+      <c r="G6" s="432"/>
       <c r="H6" s="87"/>
-      <c r="I6" s="323"/>
-      <c r="J6" s="324"/>
-      <c r="K6" s="324"/>
-      <c r="L6" s="324"/>
-      <c r="M6" s="325"/>
+      <c r="I6" s="434"/>
+      <c r="J6" s="435"/>
+      <c r="K6" s="435"/>
+      <c r="L6" s="435"/>
+      <c r="M6" s="436"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="334" t="s">
+      <c r="A7" s="438" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="335"/>
-      <c r="C7" s="335"/>
-      <c r="D7" s="335"/>
-      <c r="E7" s="335"/>
-      <c r="F7" s="335"/>
-      <c r="G7" s="335"/>
-      <c r="H7" s="336"/>
+      <c r="B7" s="439"/>
+      <c r="C7" s="439"/>
+      <c r="D7" s="439"/>
+      <c r="E7" s="439"/>
+      <c r="F7" s="439"/>
+      <c r="G7" s="439"/>
+      <c r="H7" s="440"/>
       <c r="I7" s="88" t="s">
         <v>233</v>
       </c>
@@ -8400,19 +8400,19 @@
       </c>
       <c r="C8" s="93"/>
       <c r="D8" s="93"/>
-      <c r="E8" s="340" t="s">
+      <c r="E8" s="384" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="340"/>
-      <c r="G8" s="340"/>
-      <c r="H8" s="341"/>
-      <c r="I8" s="326" t="s">
+      <c r="F8" s="384"/>
+      <c r="G8" s="384"/>
+      <c r="H8" s="385"/>
+      <c r="I8" s="437" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="319"/>
-      <c r="K8" s="319"/>
-      <c r="L8" s="319"/>
-      <c r="M8" s="320"/>
+      <c r="J8" s="389"/>
+      <c r="K8" s="389"/>
+      <c r="L8" s="389"/>
+      <c r="M8" s="390"/>
     </row>
     <row r="9" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="94" t="s">
@@ -8438,14 +8438,14 @@
       <c r="A10" s="98" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="299" t="str">
+      <c r="C10" s="416" t="str">
         <f>CONCATENATE(VLOOKUP(B8,ADDRESS!$A$2:$E$30,3,FALSE),", ",VLOOKUP(B8,ADDRESS!$A$2:$E$30,4,FALSE)," ",VLOOKUP(B8,ADDRESS!$A$2:$E$30,5,FALSE))</f>
         <v>TYLER, TX 75706</v>
       </c>
-      <c r="D10" s="299"/>
-      <c r="E10" s="299"/>
-      <c r="F10" s="299"/>
-      <c r="G10" s="299"/>
+      <c r="D10" s="416"/>
+      <c r="E10" s="416"/>
+      <c r="F10" s="416"/>
+      <c r="G10" s="416"/>
       <c r="H10" s="95"/>
       <c r="I10" s="99" t="s">
         <v>234</v>
@@ -8459,22 +8459,22 @@
       <c r="M10" s="101"/>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="342" t="s">
+      <c r="A11" s="386" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="317"/>
-      <c r="C11" s="317"/>
-      <c r="D11" s="317"/>
-      <c r="E11" s="317"/>
-      <c r="F11" s="321" t="s">
+      <c r="B11" s="387"/>
+      <c r="C11" s="387"/>
+      <c r="D11" s="387"/>
+      <c r="E11" s="387"/>
+      <c r="F11" s="432" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="321"/>
+      <c r="G11" s="432"/>
       <c r="H11" s="87"/>
-      <c r="I11" s="302" t="s">
+      <c r="I11" s="419" t="s">
         <v>75</v>
       </c>
-      <c r="J11" s="303"/>
+      <c r="J11" s="420"/>
       <c r="K11" s="102">
         <f>ADDRESS!I4</f>
         <v>523953410</v>
@@ -8483,74 +8483,74 @@
       <c r="M11" s="103"/>
     </row>
     <row r="12" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="327" t="s">
+      <c r="A12" s="355" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="328"/>
-      <c r="C12" s="328"/>
-      <c r="D12" s="328"/>
-      <c r="E12" s="328"/>
-      <c r="F12" s="328"/>
-      <c r="G12" s="328"/>
-      <c r="H12" s="329"/>
-      <c r="I12" s="322"/>
-      <c r="J12" s="300"/>
-      <c r="K12" s="300"/>
-      <c r="L12" s="300"/>
-      <c r="M12" s="301"/>
+      <c r="B12" s="356"/>
+      <c r="C12" s="356"/>
+      <c r="D12" s="356"/>
+      <c r="E12" s="356"/>
+      <c r="F12" s="356"/>
+      <c r="G12" s="356"/>
+      <c r="H12" s="357"/>
+      <c r="I12" s="433"/>
+      <c r="J12" s="417"/>
+      <c r="K12" s="417"/>
+      <c r="L12" s="417"/>
+      <c r="M12" s="418"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="313" t="s">
+      <c r="A13" s="428" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="314"/>
-      <c r="C13" s="314"/>
-      <c r="D13" s="314"/>
-      <c r="E13" s="314"/>
-      <c r="F13" s="314"/>
-      <c r="G13" s="314"/>
-      <c r="H13" s="315"/>
-      <c r="I13" s="322"/>
-      <c r="J13" s="300"/>
-      <c r="K13" s="300"/>
-      <c r="L13" s="300"/>
-      <c r="M13" s="301"/>
+      <c r="B13" s="429"/>
+      <c r="C13" s="429"/>
+      <c r="D13" s="429"/>
+      <c r="E13" s="429"/>
+      <c r="F13" s="429"/>
+      <c r="G13" s="429"/>
+      <c r="H13" s="430"/>
+      <c r="I13" s="433"/>
+      <c r="J13" s="417"/>
+      <c r="K13" s="417"/>
+      <c r="L13" s="417"/>
+      <c r="M13" s="418"/>
     </row>
     <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="318" t="s">
+      <c r="A14" s="388" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="319"/>
-      <c r="C14" s="319"/>
-      <c r="D14" s="319"/>
-      <c r="E14" s="319"/>
-      <c r="F14" s="319"/>
-      <c r="G14" s="319"/>
-      <c r="H14" s="320"/>
-      <c r="I14" s="323"/>
-      <c r="J14" s="324"/>
-      <c r="K14" s="324"/>
-      <c r="L14" s="324"/>
-      <c r="M14" s="325"/>
+      <c r="B14" s="389"/>
+      <c r="C14" s="389"/>
+      <c r="D14" s="389"/>
+      <c r="E14" s="389"/>
+      <c r="F14" s="389"/>
+      <c r="G14" s="389"/>
+      <c r="H14" s="390"/>
+      <c r="I14" s="434"/>
+      <c r="J14" s="435"/>
+      <c r="K14" s="435"/>
+      <c r="L14" s="435"/>
+      <c r="M14" s="436"/>
     </row>
     <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="350" t="s">
+      <c r="A15" s="398" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="351"/>
-      <c r="C15" s="351"/>
-      <c r="D15" s="351"/>
-      <c r="E15" s="351"/>
-      <c r="F15" s="352"/>
-      <c r="G15" s="352"/>
-      <c r="H15" s="352"/>
-      <c r="I15" s="347" t="s">
+      <c r="B15" s="399"/>
+      <c r="C15" s="399"/>
+      <c r="D15" s="399"/>
+      <c r="E15" s="399"/>
+      <c r="F15" s="400"/>
+      <c r="G15" s="400"/>
+      <c r="H15" s="400"/>
+      <c r="I15" s="395" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="348"/>
-      <c r="K15" s="348"/>
-      <c r="L15" s="348"/>
-      <c r="M15" s="349"/>
+      <c r="J15" s="396"/>
+      <c r="K15" s="396"/>
+      <c r="L15" s="396"/>
+      <c r="M15" s="397"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="70"/>
@@ -8561,13 +8561,13 @@
       <c r="F16" s="71"/>
       <c r="G16" s="71"/>
       <c r="H16" s="72"/>
-      <c r="I16" s="364" t="s">
+      <c r="I16" s="410" t="s">
         <v>61</v>
       </c>
-      <c r="J16" s="365"/>
-      <c r="K16" s="365"/>
-      <c r="L16" s="365"/>
-      <c r="M16" s="366"/>
+      <c r="J16" s="411"/>
+      <c r="K16" s="411"/>
+      <c r="L16" s="411"/>
+      <c r="M16" s="412"/>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="73" t="s">
@@ -8577,19 +8577,19 @@
       <c r="C17" s="74"/>
       <c r="D17" s="74"/>
       <c r="E17" s="74"/>
-      <c r="F17" s="300">
+      <c r="F17" s="417">
         <f>ADDRESS!I5</f>
         <v>59642884</v>
       </c>
-      <c r="G17" s="300"/>
-      <c r="H17" s="301"/>
-      <c r="I17" s="361"/>
-      <c r="J17" s="340"/>
-      <c r="K17" s="343" t="s">
+      <c r="G17" s="417"/>
+      <c r="H17" s="418"/>
+      <c r="I17" s="409"/>
+      <c r="J17" s="384"/>
+      <c r="K17" s="391" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="343"/>
-      <c r="M17" s="344"/>
+      <c r="L17" s="391"/>
+      <c r="M17" s="392"/>
     </row>
     <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="75"/>
@@ -8600,300 +8600,300 @@
       <c r="F18" s="76"/>
       <c r="G18" s="76"/>
       <c r="H18" s="77"/>
-      <c r="I18" s="362" t="s">
+      <c r="I18" s="305" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="363"/>
-      <c r="K18" s="345"/>
-      <c r="L18" s="345"/>
-      <c r="M18" s="346"/>
+      <c r="J18" s="306"/>
+      <c r="K18" s="393"/>
+      <c r="L18" s="393"/>
+      <c r="M18" s="394"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="373" t="s">
+      <c r="A19" s="358" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="374"/>
-      <c r="C19" s="374"/>
-      <c r="D19" s="374"/>
-      <c r="E19" s="374"/>
-      <c r="F19" s="374"/>
-      <c r="G19" s="374"/>
-      <c r="H19" s="374"/>
-      <c r="I19" s="374"/>
-      <c r="J19" s="374"/>
-      <c r="K19" s="374"/>
-      <c r="L19" s="374"/>
-      <c r="M19" s="375"/>
+      <c r="B19" s="359"/>
+      <c r="C19" s="359"/>
+      <c r="D19" s="359"/>
+      <c r="E19" s="359"/>
+      <c r="F19" s="359"/>
+      <c r="G19" s="359"/>
+      <c r="H19" s="359"/>
+      <c r="I19" s="359"/>
+      <c r="J19" s="359"/>
+      <c r="K19" s="359"/>
+      <c r="L19" s="359"/>
+      <c r="M19" s="360"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="376" t="s">
+      <c r="A20" s="413" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="377"/>
-      <c r="C20" s="377"/>
-      <c r="D20" s="377"/>
-      <c r="E20" s="377" t="s">
+      <c r="B20" s="414"/>
+      <c r="C20" s="414"/>
+      <c r="D20" s="414"/>
+      <c r="E20" s="414" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="377" t="s">
+      <c r="F20" s="414" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="377"/>
-      <c r="H20" s="359" t="s">
+      <c r="G20" s="414"/>
+      <c r="H20" s="407" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="360"/>
-      <c r="J20" s="353" t="s">
+      <c r="I20" s="408"/>
+      <c r="J20" s="401" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="354"/>
-      <c r="L20" s="354"/>
-      <c r="M20" s="355"/>
+      <c r="K20" s="402"/>
+      <c r="L20" s="402"/>
+      <c r="M20" s="403"/>
     </row>
     <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="376"/>
-      <c r="B21" s="377"/>
-      <c r="C21" s="377"/>
-      <c r="D21" s="377"/>
-      <c r="E21" s="377"/>
-      <c r="F21" s="377"/>
-      <c r="G21" s="377"/>
-      <c r="H21" s="337" t="s">
+      <c r="A21" s="413"/>
+      <c r="B21" s="414"/>
+      <c r="C21" s="414"/>
+      <c r="D21" s="414"/>
+      <c r="E21" s="414"/>
+      <c r="F21" s="414"/>
+      <c r="G21" s="414"/>
+      <c r="H21" s="441" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="338"/>
-      <c r="J21" s="356"/>
-      <c r="K21" s="357"/>
-      <c r="L21" s="357"/>
-      <c r="M21" s="358"/>
+      <c r="I21" s="442"/>
+      <c r="J21" s="404"/>
+      <c r="K21" s="405"/>
+      <c r="L21" s="405"/>
+      <c r="M21" s="406"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="378" t="str">
+      <c r="A22" s="415" t="str">
         <f>VLOOKUP(B8,'Customer Order Info'!$A$3:$D$31,2,FALSE)</f>
         <v>0215-8880831-0578</v>
       </c>
-      <c r="B22" s="333"/>
-      <c r="C22" s="333"/>
-      <c r="D22" s="369"/>
+      <c r="B22" s="198"/>
+      <c r="C22" s="198"/>
+      <c r="D22" s="285"/>
       <c r="E22" s="10">
         <f>VLOOKUP(A22,'Customer Order Info'!B3:D31,2,FALSE)</f>
         <v>83</v>
       </c>
-      <c r="F22" s="333">
+      <c r="F22" s="198">
         <f>VLOOKUP(A22,'Customer Order Info'!B3:D31,3,FALSE)</f>
         <v>83</v>
       </c>
-      <c r="G22" s="333"/>
+      <c r="G22" s="198"/>
       <c r="H22" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="333"/>
-      <c r="K22" s="333"/>
-      <c r="L22" s="333"/>
-      <c r="M22" s="339"/>
+      <c r="J22" s="198"/>
+      <c r="K22" s="198"/>
+      <c r="L22" s="198"/>
+      <c r="M22" s="375"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="330"/>
-      <c r="B23" s="331"/>
-      <c r="C23" s="331"/>
-      <c r="D23" s="332"/>
+      <c r="A23" s="378"/>
+      <c r="B23" s="379"/>
+      <c r="C23" s="379"/>
+      <c r="D23" s="380"/>
       <c r="E23" s="10"/>
-      <c r="F23" s="333"/>
-      <c r="G23" s="333"/>
+      <c r="F23" s="198"/>
+      <c r="G23" s="198"/>
       <c r="H23" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="333"/>
-      <c r="K23" s="333"/>
-      <c r="L23" s="333"/>
-      <c r="M23" s="339"/>
+      <c r="J23" s="198"/>
+      <c r="K23" s="198"/>
+      <c r="L23" s="198"/>
+      <c r="M23" s="375"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="330"/>
-      <c r="B24" s="331"/>
-      <c r="C24" s="331"/>
-      <c r="D24" s="332"/>
+      <c r="A24" s="378"/>
+      <c r="B24" s="379"/>
+      <c r="C24" s="379"/>
+      <c r="D24" s="380"/>
       <c r="E24" s="10"/>
-      <c r="F24" s="333"/>
-      <c r="G24" s="333"/>
+      <c r="F24" s="198"/>
+      <c r="G24" s="198"/>
       <c r="H24" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="333"/>
-      <c r="K24" s="333"/>
-      <c r="L24" s="333"/>
-      <c r="M24" s="339"/>
+      <c r="J24" s="198"/>
+      <c r="K24" s="198"/>
+      <c r="L24" s="198"/>
+      <c r="M24" s="375"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="330"/>
-      <c r="B25" s="331"/>
-      <c r="C25" s="331"/>
-      <c r="D25" s="332"/>
+      <c r="A25" s="378"/>
+      <c r="B25" s="379"/>
+      <c r="C25" s="379"/>
+      <c r="D25" s="380"/>
       <c r="E25" s="10"/>
-      <c r="F25" s="333"/>
-      <c r="G25" s="333"/>
+      <c r="F25" s="198"/>
+      <c r="G25" s="198"/>
       <c r="H25" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="333"/>
-      <c r="K25" s="333"/>
-      <c r="L25" s="333"/>
-      <c r="M25" s="339"/>
+      <c r="J25" s="198"/>
+      <c r="K25" s="198"/>
+      <c r="L25" s="198"/>
+      <c r="M25" s="375"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="330"/>
-      <c r="B26" s="331"/>
-      <c r="C26" s="331"/>
-      <c r="D26" s="332"/>
+      <c r="A26" s="378"/>
+      <c r="B26" s="379"/>
+      <c r="C26" s="379"/>
+      <c r="D26" s="380"/>
       <c r="E26" s="10"/>
-      <c r="F26" s="333"/>
-      <c r="G26" s="333"/>
+      <c r="F26" s="198"/>
+      <c r="G26" s="198"/>
       <c r="H26" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="333"/>
-      <c r="K26" s="333"/>
-      <c r="L26" s="333"/>
-      <c r="M26" s="339"/>
+      <c r="J26" s="198"/>
+      <c r="K26" s="198"/>
+      <c r="L26" s="198"/>
+      <c r="M26" s="375"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="330"/>
-      <c r="B27" s="331"/>
-      <c r="C27" s="331"/>
-      <c r="D27" s="332"/>
+      <c r="A27" s="378"/>
+      <c r="B27" s="379"/>
+      <c r="C27" s="379"/>
+      <c r="D27" s="380"/>
       <c r="E27" s="10"/>
-      <c r="F27" s="333"/>
-      <c r="G27" s="333"/>
+      <c r="F27" s="198"/>
+      <c r="G27" s="198"/>
       <c r="H27" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J27" s="333"/>
-      <c r="K27" s="333"/>
-      <c r="L27" s="333"/>
-      <c r="M27" s="339"/>
+      <c r="J27" s="198"/>
+      <c r="K27" s="198"/>
+      <c r="L27" s="198"/>
+      <c r="M27" s="375"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="330"/>
-      <c r="B28" s="331"/>
-      <c r="C28" s="331"/>
-      <c r="D28" s="332"/>
+      <c r="A28" s="378"/>
+      <c r="B28" s="379"/>
+      <c r="C28" s="379"/>
+      <c r="D28" s="380"/>
       <c r="E28" s="10"/>
-      <c r="F28" s="333"/>
-      <c r="G28" s="333"/>
+      <c r="F28" s="198"/>
+      <c r="G28" s="198"/>
       <c r="H28" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J28" s="333"/>
-      <c r="K28" s="333"/>
-      <c r="L28" s="333"/>
-      <c r="M28" s="339"/>
+      <c r="J28" s="198"/>
+      <c r="K28" s="198"/>
+      <c r="L28" s="198"/>
+      <c r="M28" s="375"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="330"/>
-      <c r="B29" s="331"/>
-      <c r="C29" s="331"/>
-      <c r="D29" s="332"/>
+      <c r="A29" s="378"/>
+      <c r="B29" s="379"/>
+      <c r="C29" s="379"/>
+      <c r="D29" s="380"/>
       <c r="E29" s="10"/>
-      <c r="F29" s="333"/>
-      <c r="G29" s="333"/>
+      <c r="F29" s="198"/>
+      <c r="G29" s="198"/>
       <c r="H29" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J29" s="333"/>
-      <c r="K29" s="333"/>
-      <c r="L29" s="333"/>
-      <c r="M29" s="339"/>
+      <c r="J29" s="198"/>
+      <c r="K29" s="198"/>
+      <c r="L29" s="198"/>
+      <c r="M29" s="375"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="367" t="s">
+      <c r="A30" s="376" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="368"/>
-      <c r="C30" s="368"/>
-      <c r="D30" s="368"/>
+      <c r="B30" s="377"/>
+      <c r="C30" s="377"/>
+      <c r="D30" s="377"/>
       <c r="E30" s="9">
         <f>SUM(E22:E29)</f>
         <v>83</v>
       </c>
-      <c r="F30" s="379">
+      <c r="F30" s="364">
         <f>SUM(F22:G29)</f>
         <v>83</v>
       </c>
-      <c r="G30" s="333"/>
-      <c r="H30" s="306"/>
-      <c r="I30" s="307"/>
-      <c r="J30" s="306"/>
-      <c r="K30" s="372"/>
-      <c r="L30" s="372"/>
-      <c r="M30" s="307"/>
+      <c r="G30" s="198"/>
+      <c r="H30" s="381"/>
+      <c r="I30" s="383"/>
+      <c r="J30" s="381"/>
+      <c r="K30" s="382"/>
+      <c r="L30" s="382"/>
+      <c r="M30" s="383"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="380" t="s">
+      <c r="A31" s="365" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="381"/>
-      <c r="C31" s="381"/>
-      <c r="D31" s="381"/>
-      <c r="E31" s="381"/>
-      <c r="F31" s="381"/>
-      <c r="G31" s="381"/>
-      <c r="H31" s="381"/>
-      <c r="I31" s="381"/>
-      <c r="J31" s="381"/>
-      <c r="K31" s="381"/>
-      <c r="L31" s="381"/>
-      <c r="M31" s="382"/>
+      <c r="B31" s="366"/>
+      <c r="C31" s="366"/>
+      <c r="D31" s="366"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
+      <c r="G31" s="366"/>
+      <c r="H31" s="366"/>
+      <c r="I31" s="366"/>
+      <c r="J31" s="366"/>
+      <c r="K31" s="366"/>
+      <c r="L31" s="366"/>
+      <c r="M31" s="367"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="387" t="s">
+      <c r="A32" s="372" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="385"/>
-      <c r="C32" s="385" t="s">
+      <c r="B32" s="370"/>
+      <c r="C32" s="370" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="385"/>
-      <c r="E32" s="388" t="s">
+      <c r="D32" s="370"/>
+      <c r="E32" s="373" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="389" t="s">
+      <c r="F32" s="374" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="383" t="s">
+      <c r="G32" s="368" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="383"/>
-      <c r="I32" s="383"/>
-      <c r="J32" s="383"/>
-      <c r="K32" s="383"/>
-      <c r="L32" s="385" t="s">
+      <c r="H32" s="368"/>
+      <c r="I32" s="368"/>
+      <c r="J32" s="368"/>
+      <c r="K32" s="368"/>
+      <c r="L32" s="370" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="386"/>
+      <c r="M32" s="371"/>
     </row>
     <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
@@ -8908,15 +8908,15 @@
       <c r="D33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="388"/>
-      <c r="F33" s="389"/>
-      <c r="G33" s="384" t="s">
+      <c r="E33" s="373"/>
+      <c r="F33" s="374"/>
+      <c r="G33" s="369" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="384"/>
-      <c r="I33" s="384"/>
-      <c r="J33" s="384"/>
-      <c r="K33" s="384"/>
+      <c r="H33" s="369"/>
+      <c r="I33" s="369"/>
+      <c r="J33" s="369"/>
+      <c r="K33" s="369"/>
       <c r="L33" s="2" t="s">
         <v>14</v>
       </c>
@@ -8944,13 +8944,13 @@
         <v>83</v>
       </c>
       <c r="F34" s="10"/>
-      <c r="G34" s="369" t="s">
+      <c r="G34" s="285" t="s">
         <v>77</v>
       </c>
-      <c r="H34" s="370"/>
-      <c r="I34" s="370"/>
-      <c r="J34" s="370"/>
-      <c r="K34" s="371"/>
+      <c r="H34" s="343"/>
+      <c r="I34" s="343"/>
+      <c r="J34" s="343"/>
+      <c r="K34" s="286"/>
       <c r="L34" s="106"/>
       <c r="M34" s="107"/>
     </row>
@@ -8961,11 +8961,11 @@
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
       <c r="F35" s="106"/>
-      <c r="G35" s="369"/>
-      <c r="H35" s="370"/>
-      <c r="I35" s="370"/>
-      <c r="J35" s="370"/>
-      <c r="K35" s="371"/>
+      <c r="G35" s="285"/>
+      <c r="H35" s="343"/>
+      <c r="I35" s="343"/>
+      <c r="J35" s="343"/>
+      <c r="K35" s="286"/>
       <c r="L35" s="106"/>
       <c r="M35" s="107"/>
     </row>
@@ -8976,11 +8976,11 @@
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
       <c r="F36" s="106"/>
-      <c r="G36" s="369"/>
-      <c r="H36" s="370"/>
-      <c r="I36" s="370"/>
-      <c r="J36" s="370"/>
-      <c r="K36" s="371"/>
+      <c r="G36" s="285"/>
+      <c r="H36" s="343"/>
+      <c r="I36" s="343"/>
+      <c r="J36" s="343"/>
+      <c r="K36" s="286"/>
       <c r="L36" s="106"/>
       <c r="M36" s="107"/>
     </row>
@@ -8991,19 +8991,19 @@
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
       <c r="F37" s="106"/>
-      <c r="G37" s="369"/>
-      <c r="H37" s="370"/>
-      <c r="I37" s="370"/>
-      <c r="J37" s="370"/>
-      <c r="K37" s="371"/>
+      <c r="G37" s="285"/>
+      <c r="H37" s="343"/>
+      <c r="I37" s="343"/>
+      <c r="J37" s="343"/>
+      <c r="K37" s="286"/>
       <c r="L37" s="106"/>
       <c r="M37" s="107"/>
-      <c r="Q37" s="391"/>
-      <c r="R37" s="391"/>
+      <c r="Q37" s="334"/>
+      <c r="R37" s="334"/>
       <c r="S37" s="7"/>
-      <c r="T37" s="390"/>
-      <c r="U37" s="390"/>
-      <c r="V37" s="390"/>
+      <c r="T37" s="311"/>
+      <c r="U37" s="311"/>
+      <c r="V37" s="311"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A38" s="108"/>
@@ -9012,19 +9012,19 @@
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
       <c r="F38" s="106"/>
-      <c r="G38" s="369"/>
-      <c r="H38" s="370"/>
-      <c r="I38" s="370"/>
-      <c r="J38" s="370"/>
-      <c r="K38" s="371"/>
+      <c r="G38" s="285"/>
+      <c r="H38" s="343"/>
+      <c r="I38" s="343"/>
+      <c r="J38" s="343"/>
+      <c r="K38" s="286"/>
       <c r="L38" s="106"/>
       <c r="M38" s="109"/>
-      <c r="Q38" s="391"/>
-      <c r="R38" s="391"/>
+      <c r="Q38" s="334"/>
+      <c r="R38" s="334"/>
       <c r="S38" s="7"/>
-      <c r="T38" s="390"/>
-      <c r="U38" s="390"/>
-      <c r="V38" s="390"/>
+      <c r="T38" s="311"/>
+      <c r="U38" s="311"/>
+      <c r="V38" s="311"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A39" s="108"/>
@@ -9033,19 +9033,19 @@
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
       <c r="F39" s="106"/>
-      <c r="G39" s="369"/>
-      <c r="H39" s="370"/>
-      <c r="I39" s="370"/>
-      <c r="J39" s="370"/>
-      <c r="K39" s="371"/>
+      <c r="G39" s="285"/>
+      <c r="H39" s="343"/>
+      <c r="I39" s="343"/>
+      <c r="J39" s="343"/>
+      <c r="K39" s="286"/>
       <c r="L39" s="106"/>
       <c r="M39" s="109"/>
       <c r="Q39" s="6"/>
       <c r="R39" s="6"/>
-      <c r="S39" s="392"/>
-      <c r="T39" s="390"/>
-      <c r="U39" s="390"/>
-      <c r="V39" s="390"/>
+      <c r="S39" s="337"/>
+      <c r="T39" s="311"/>
+      <c r="U39" s="311"/>
+      <c r="V39" s="311"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A40" s="108"/>
@@ -9054,19 +9054,19 @@
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
       <c r="F40" s="106"/>
-      <c r="G40" s="369"/>
-      <c r="H40" s="370"/>
-      <c r="I40" s="370"/>
-      <c r="J40" s="370"/>
-      <c r="K40" s="371"/>
+      <c r="G40" s="285"/>
+      <c r="H40" s="343"/>
+      <c r="I40" s="343"/>
+      <c r="J40" s="343"/>
+      <c r="K40" s="286"/>
       <c r="L40" s="106"/>
       <c r="M40" s="107"/>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
-      <c r="S40" s="392"/>
-      <c r="T40" s="390"/>
-      <c r="U40" s="390"/>
-      <c r="V40" s="390"/>
+      <c r="S40" s="337"/>
+      <c r="T40" s="311"/>
+      <c r="U40" s="311"/>
+      <c r="V40" s="311"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A41" s="108"/>
@@ -9075,11 +9075,11 @@
       <c r="D41" s="10"/>
       <c r="E41" s="10"/>
       <c r="F41" s="106"/>
-      <c r="G41" s="369"/>
-      <c r="H41" s="370"/>
-      <c r="I41" s="370"/>
-      <c r="J41" s="370"/>
-      <c r="K41" s="371"/>
+      <c r="G41" s="285"/>
+      <c r="H41" s="343"/>
+      <c r="I41" s="343"/>
+      <c r="J41" s="343"/>
+      <c r="K41" s="286"/>
       <c r="L41" s="106"/>
       <c r="M41" s="107"/>
     </row>
@@ -9099,291 +9099,291 @@
         <v>83</v>
       </c>
       <c r="F42" s="113"/>
-      <c r="G42" s="399" t="s">
+      <c r="G42" s="344" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="400"/>
-      <c r="I42" s="400"/>
-      <c r="J42" s="400"/>
-      <c r="K42" s="401"/>
+      <c r="H42" s="345"/>
+      <c r="I42" s="345"/>
+      <c r="J42" s="345"/>
+      <c r="K42" s="346"/>
       <c r="L42" s="113"/>
       <c r="M42" s="114"/>
     </row>
     <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="409" t="s">
+      <c r="A43" s="313" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="410"/>
-      <c r="C43" s="410"/>
-      <c r="D43" s="410"/>
-      <c r="E43" s="410"/>
-      <c r="F43" s="410"/>
-      <c r="G43" s="410"/>
-      <c r="H43" s="411"/>
-      <c r="I43" s="327" t="s">
+      <c r="B43" s="314"/>
+      <c r="C43" s="314"/>
+      <c r="D43" s="314"/>
+      <c r="E43" s="314"/>
+      <c r="F43" s="314"/>
+      <c r="G43" s="314"/>
+      <c r="H43" s="315"/>
+      <c r="I43" s="355" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="328"/>
-      <c r="K43" s="328"/>
-      <c r="L43" s="328"/>
-      <c r="M43" s="329"/>
+      <c r="J43" s="356"/>
+      <c r="K43" s="356"/>
+      <c r="L43" s="356"/>
+      <c r="M43" s="357"/>
     </row>
     <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="412"/>
-      <c r="B44" s="413"/>
-      <c r="C44" s="413"/>
-      <c r="D44" s="413"/>
-      <c r="E44" s="413"/>
-      <c r="F44" s="413"/>
-      <c r="G44" s="413"/>
-      <c r="H44" s="414"/>
-      <c r="I44" s="373"/>
-      <c r="J44" s="374"/>
-      <c r="K44" s="374"/>
-      <c r="L44" s="374"/>
-      <c r="M44" s="375"/>
+      <c r="A44" s="316"/>
+      <c r="B44" s="317"/>
+      <c r="C44" s="317"/>
+      <c r="D44" s="317"/>
+      <c r="E44" s="317"/>
+      <c r="F44" s="317"/>
+      <c r="G44" s="317"/>
+      <c r="H44" s="318"/>
+      <c r="I44" s="358"/>
+      <c r="J44" s="359"/>
+      <c r="K44" s="359"/>
+      <c r="L44" s="359"/>
+      <c r="M44" s="360"/>
     </row>
     <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="425" t="s">
+      <c r="A45" s="319" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="426"/>
-      <c r="C45" s="426"/>
-      <c r="D45" s="426"/>
-      <c r="E45" s="426"/>
-      <c r="F45" s="426"/>
-      <c r="G45" s="426"/>
-      <c r="H45" s="427"/>
-      <c r="I45" s="417" t="s">
+      <c r="B45" s="320"/>
+      <c r="C45" s="320"/>
+      <c r="D45" s="320"/>
+      <c r="E45" s="320"/>
+      <c r="F45" s="320"/>
+      <c r="G45" s="320"/>
+      <c r="H45" s="321"/>
+      <c r="I45" s="361" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="418"/>
-      <c r="K45" s="418"/>
-      <c r="L45" s="418"/>
-      <c r="M45" s="419"/>
+      <c r="J45" s="362"/>
+      <c r="K45" s="362"/>
+      <c r="L45" s="362"/>
+      <c r="M45" s="363"/>
     </row>
     <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="425" t="s">
+      <c r="A46" s="319" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="426"/>
-      <c r="C46" s="426"/>
-      <c r="D46" s="426"/>
-      <c r="E46" s="426"/>
-      <c r="F46" s="426"/>
-      <c r="G46" s="426"/>
-      <c r="H46" s="427"/>
-      <c r="I46" s="417"/>
-      <c r="J46" s="418"/>
-      <c r="K46" s="418"/>
-      <c r="L46" s="418"/>
-      <c r="M46" s="419"/>
+      <c r="B46" s="320"/>
+      <c r="C46" s="320"/>
+      <c r="D46" s="320"/>
+      <c r="E46" s="320"/>
+      <c r="F46" s="320"/>
+      <c r="G46" s="320"/>
+      <c r="H46" s="321"/>
+      <c r="I46" s="361"/>
+      <c r="J46" s="362"/>
+      <c r="K46" s="362"/>
+      <c r="L46" s="362"/>
+      <c r="M46" s="363"/>
     </row>
     <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="428"/>
-      <c r="B47" s="429"/>
-      <c r="C47" s="429"/>
-      <c r="D47" s="429"/>
-      <c r="E47" s="429"/>
-      <c r="F47" s="429"/>
-      <c r="G47" s="429"/>
-      <c r="H47" s="430"/>
-      <c r="I47" s="421" t="s">
+      <c r="A47" s="322"/>
+      <c r="B47" s="323"/>
+      <c r="C47" s="323"/>
+      <c r="D47" s="323"/>
+      <c r="E47" s="323"/>
+      <c r="F47" s="323"/>
+      <c r="G47" s="323"/>
+      <c r="H47" s="324"/>
+      <c r="I47" s="308" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="422"/>
-      <c r="K47" s="422"/>
-      <c r="L47" s="422"/>
-      <c r="M47" s="423"/>
+      <c r="J47" s="309"/>
+      <c r="K47" s="309"/>
+      <c r="L47" s="309"/>
+      <c r="M47" s="310"/>
     </row>
     <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="402" t="s">
+      <c r="A48" s="329" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="393"/>
-      <c r="C48" s="393"/>
-      <c r="D48" s="393"/>
-      <c r="E48" s="393"/>
-      <c r="F48" s="393"/>
-      <c r="G48" s="393"/>
-      <c r="H48" s="393"/>
-      <c r="I48" s="393"/>
-      <c r="J48" s="393"/>
-      <c r="K48" s="393"/>
-      <c r="L48" s="393"/>
-      <c r="M48" s="394"/>
+      <c r="B48" s="330"/>
+      <c r="C48" s="330"/>
+      <c r="D48" s="330"/>
+      <c r="E48" s="330"/>
+      <c r="F48" s="330"/>
+      <c r="G48" s="330"/>
+      <c r="H48" s="330"/>
+      <c r="I48" s="330"/>
+      <c r="J48" s="330"/>
+      <c r="K48" s="330"/>
+      <c r="L48" s="330"/>
+      <c r="M48" s="338"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="409" t="s">
+      <c r="A49" s="313" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="410"/>
-      <c r="C49" s="410"/>
-      <c r="D49" s="410"/>
-      <c r="E49" s="410"/>
-      <c r="F49" s="410"/>
-      <c r="G49" s="410"/>
-      <c r="H49" s="411"/>
-      <c r="I49" s="403" t="s">
+      <c r="B49" s="314"/>
+      <c r="C49" s="314"/>
+      <c r="D49" s="314"/>
+      <c r="E49" s="314"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="315"/>
+      <c r="I49" s="347" t="s">
         <v>40</v>
       </c>
-      <c r="J49" s="404"/>
-      <c r="K49" s="404"/>
-      <c r="L49" s="404"/>
-      <c r="M49" s="405"/>
+      <c r="J49" s="348"/>
+      <c r="K49" s="348"/>
+      <c r="L49" s="348"/>
+      <c r="M49" s="349"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="412"/>
-      <c r="B50" s="413"/>
-      <c r="C50" s="413"/>
-      <c r="D50" s="413"/>
-      <c r="E50" s="413"/>
-      <c r="F50" s="413"/>
-      <c r="G50" s="413"/>
-      <c r="H50" s="414"/>
-      <c r="I50" s="406"/>
-      <c r="J50" s="407"/>
-      <c r="K50" s="407"/>
-      <c r="L50" s="407"/>
-      <c r="M50" s="408"/>
+      <c r="A50" s="316"/>
+      <c r="B50" s="317"/>
+      <c r="C50" s="317"/>
+      <c r="D50" s="317"/>
+      <c r="E50" s="317"/>
+      <c r="F50" s="317"/>
+      <c r="G50" s="317"/>
+      <c r="H50" s="318"/>
+      <c r="I50" s="350"/>
+      <c r="J50" s="351"/>
+      <c r="K50" s="351"/>
+      <c r="L50" s="351"/>
+      <c r="M50" s="352"/>
     </row>
     <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="415"/>
-      <c r="B51" s="416"/>
-      <c r="C51" s="416"/>
-      <c r="D51" s="416"/>
-      <c r="E51" s="413"/>
-      <c r="F51" s="413"/>
-      <c r="G51" s="413"/>
-      <c r="H51" s="414"/>
-      <c r="I51" s="431" t="s">
+      <c r="A51" s="353"/>
+      <c r="B51" s="354"/>
+      <c r="C51" s="354"/>
+      <c r="D51" s="354"/>
+      <c r="E51" s="317"/>
+      <c r="F51" s="317"/>
+      <c r="G51" s="317"/>
+      <c r="H51" s="318"/>
+      <c r="I51" s="325" t="s">
         <v>41</v>
       </c>
-      <c r="J51" s="432"/>
-      <c r="K51" s="433"/>
-      <c r="L51" s="433"/>
-      <c r="M51" s="434"/>
+      <c r="J51" s="326"/>
+      <c r="K51" s="327"/>
+      <c r="L51" s="327"/>
+      <c r="M51" s="328"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="402" t="s">
+      <c r="A52" s="329" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="393"/>
-      <c r="C52" s="393"/>
-      <c r="D52" s="393"/>
+      <c r="B52" s="330"/>
+      <c r="C52" s="330"/>
+      <c r="D52" s="330"/>
       <c r="E52" s="115" t="s">
         <v>44</v>
       </c>
       <c r="F52" s="116"/>
-      <c r="G52" s="438" t="s">
+      <c r="G52" s="335" t="s">
         <v>45</v>
       </c>
-      <c r="H52" s="438"/>
-      <c r="I52" s="438"/>
-      <c r="J52" s="439"/>
-      <c r="K52" s="393" t="s">
+      <c r="H52" s="335"/>
+      <c r="I52" s="335"/>
+      <c r="J52" s="336"/>
+      <c r="K52" s="330" t="s">
         <v>50</v>
       </c>
-      <c r="L52" s="393"/>
-      <c r="M52" s="394"/>
+      <c r="L52" s="330"/>
+      <c r="M52" s="338"/>
     </row>
     <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="435" t="s">
+      <c r="A53" s="331" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="436"/>
-      <c r="C53" s="436"/>
-      <c r="D53" s="436"/>
+      <c r="B53" s="332"/>
+      <c r="C53" s="332"/>
+      <c r="D53" s="332"/>
       <c r="E53" s="98"/>
       <c r="J53" s="95"/>
-      <c r="K53" s="395" t="s">
+      <c r="K53" s="339" t="s">
         <v>52</v>
       </c>
-      <c r="L53" s="395"/>
-      <c r="M53" s="396"/>
+      <c r="L53" s="339"/>
+      <c r="M53" s="340"/>
     </row>
     <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="435"/>
-      <c r="B54" s="436"/>
-      <c r="C54" s="436"/>
-      <c r="D54" s="436"/>
-      <c r="E54" s="437" t="s">
+      <c r="A54" s="331"/>
+      <c r="B54" s="332"/>
+      <c r="C54" s="332"/>
+      <c r="D54" s="332"/>
+      <c r="E54" s="333" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="391"/>
+      <c r="F54" s="334"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="390" t="s">
+      <c r="H54" s="311" t="s">
         <v>46</v>
       </c>
-      <c r="I54" s="390"/>
-      <c r="J54" s="424"/>
-      <c r="K54" s="395"/>
-      <c r="L54" s="395"/>
-      <c r="M54" s="396"/>
+      <c r="I54" s="311"/>
+      <c r="J54" s="312"/>
+      <c r="K54" s="339"/>
+      <c r="L54" s="339"/>
+      <c r="M54" s="340"/>
     </row>
     <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="435"/>
-      <c r="B55" s="436"/>
-      <c r="C55" s="436"/>
-      <c r="D55" s="436"/>
-      <c r="E55" s="437" t="s">
+      <c r="A55" s="331"/>
+      <c r="B55" s="332"/>
+      <c r="C55" s="332"/>
+      <c r="D55" s="332"/>
+      <c r="E55" s="333" t="s">
         <v>47</v>
       </c>
-      <c r="F55" s="391"/>
-      <c r="G55" s="391"/>
-      <c r="H55" s="390" t="s">
+      <c r="F55" s="334"/>
+      <c r="G55" s="334"/>
+      <c r="H55" s="311" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="390"/>
-      <c r="J55" s="424"/>
-      <c r="K55" s="395"/>
-      <c r="L55" s="395"/>
-      <c r="M55" s="396"/>
+      <c r="I55" s="311"/>
+      <c r="J55" s="312"/>
+      <c r="K55" s="339"/>
+      <c r="L55" s="339"/>
+      <c r="M55" s="340"/>
     </row>
     <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="98"/>
       <c r="D56" s="95"/>
-      <c r="E56" s="437"/>
-      <c r="F56" s="391"/>
-      <c r="G56" s="391"/>
-      <c r="H56" s="390"/>
-      <c r="I56" s="390"/>
-      <c r="J56" s="424"/>
-      <c r="K56" s="397" t="s">
+      <c r="E56" s="333"/>
+      <c r="F56" s="334"/>
+      <c r="G56" s="334"/>
+      <c r="H56" s="311"/>
+      <c r="I56" s="311"/>
+      <c r="J56" s="312"/>
+      <c r="K56" s="341" t="s">
         <v>51</v>
       </c>
-      <c r="L56" s="397"/>
-      <c r="M56" s="398"/>
+      <c r="L56" s="341"/>
+      <c r="M56" s="342"/>
     </row>
     <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="98"/>
       <c r="D57" s="95"/>
-      <c r="E57" s="437"/>
-      <c r="F57" s="391"/>
+      <c r="E57" s="333"/>
+      <c r="F57" s="334"/>
       <c r="G57" s="7"/>
-      <c r="H57" s="390" t="s">
+      <c r="H57" s="311" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="390"/>
-      <c r="J57" s="424"/>
+      <c r="I57" s="311"/>
+      <c r="J57" s="312"/>
       <c r="K57" s="117"/>
       <c r="L57" s="118"/>
       <c r="M57" s="119"/>
     </row>
     <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="120"/>
-      <c r="B58" s="305">
+      <c r="B58" s="422">
         <f>B1</f>
         <v>45877</v>
       </c>
-      <c r="C58" s="305"/>
+      <c r="C58" s="422"/>
       <c r="D58" s="87"/>
-      <c r="E58" s="362"/>
-      <c r="F58" s="363"/>
-      <c r="G58" s="363"/>
-      <c r="H58" s="363"/>
-      <c r="I58" s="363"/>
-      <c r="J58" s="420"/>
+      <c r="E58" s="305"/>
+      <c r="F58" s="306"/>
+      <c r="G58" s="306"/>
+      <c r="H58" s="306"/>
+      <c r="I58" s="306"/>
+      <c r="J58" s="307"/>
       <c r="K58" s="121"/>
       <c r="L58" s="122"/>
       <c r="M58" s="123"/>
@@ -9402,69 +9402,29 @@
     </row>
   </sheetData>
   <mergeCells count="110">
-    <mergeCell ref="E58:J58"/>
-    <mergeCell ref="I47:M47"/>
-    <mergeCell ref="H55:J56"/>
-    <mergeCell ref="A43:H44"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A46:H47"/>
-    <mergeCell ref="I51:M51"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A53:D55"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="H57:J57"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="E55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="G52:J52"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="T37:V37"/>
-    <mergeCell ref="T38:V38"/>
-    <mergeCell ref="T39:V40"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="S39:S40"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="K53:M55"/>
-    <mergeCell ref="K56:M56"/>
-    <mergeCell ref="G37:K37"/>
-    <mergeCell ref="G42:K42"/>
-    <mergeCell ref="G40:K40"/>
-    <mergeCell ref="A48:M48"/>
-    <mergeCell ref="I49:M50"/>
-    <mergeCell ref="G41:K41"/>
-    <mergeCell ref="G38:K38"/>
-    <mergeCell ref="A49:H51"/>
-    <mergeCell ref="I43:M44"/>
-    <mergeCell ref="I45:M46"/>
-    <mergeCell ref="G39:K39"/>
-    <mergeCell ref="G35:K35"/>
-    <mergeCell ref="G36:K36"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="A31:M31"/>
-    <mergeCell ref="G32:K32"/>
-    <mergeCell ref="G33:K33"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="G34:K34"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="I4:M6"/>
+    <mergeCell ref="I12:M14"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J29:M29"/>
     <mergeCell ref="E8:H8"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A4:H4"/>
@@ -9489,29 +9449,69 @@
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C10:G10"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="I4:M6"/>
-    <mergeCell ref="I12:M14"/>
-    <mergeCell ref="I8:M8"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="G32:K32"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="G34:K34"/>
+    <mergeCell ref="T37:V37"/>
+    <mergeCell ref="T38:V38"/>
+    <mergeCell ref="T39:V40"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="S39:S40"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="K53:M55"/>
+    <mergeCell ref="K56:M56"/>
+    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="G40:K40"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="I49:M50"/>
+    <mergeCell ref="G41:K41"/>
+    <mergeCell ref="G38:K38"/>
+    <mergeCell ref="A49:H51"/>
+    <mergeCell ref="I43:M44"/>
+    <mergeCell ref="I45:M46"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="E58:J58"/>
+    <mergeCell ref="I47:M47"/>
+    <mergeCell ref="H55:J56"/>
+    <mergeCell ref="A43:H44"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A46:H47"/>
+    <mergeCell ref="I51:M51"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A53:D55"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="H57:J57"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="E55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="G52:J52"/>
+    <mergeCell ref="E54:F54"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.26" top="0.52" bottom="0.56000000000000005" header="0.5" footer="0.5"/>
@@ -9561,10 +9561,10 @@
       <c r="E1" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="H1" s="440" t="s">
+      <c r="H1" s="125" t="s">
         <v>226</v>
       </c>
-      <c r="I1" s="440" t="s">
+      <c r="I1" s="125" t="s">
         <v>227</v>
       </c>
     </row>
@@ -9584,10 +9584,10 @@
       <c r="E2">
         <v>92336</v>
       </c>
-      <c r="H2" s="440" t="s">
+      <c r="H2" s="125" t="s">
         <v>230</v>
       </c>
-      <c r="I2" s="440" t="s">
+      <c r="I2" s="125" t="s">
         <v>231</v>
       </c>
     </row>
@@ -9607,10 +9607,10 @@
       <c r="E3">
         <v>81001</v>
       </c>
-      <c r="H3" s="440" t="s">
+      <c r="H3" s="125" t="s">
         <v>228</v>
       </c>
-      <c r="I3" s="440">
+      <c r="I3" s="125">
         <v>10285609</v>
       </c>
     </row>
@@ -9630,10 +9630,10 @@
       <c r="E4">
         <v>24477</v>
       </c>
-      <c r="H4" s="440" t="s">
+      <c r="H4" s="125" t="s">
         <v>229</v>
       </c>
-      <c r="I4" s="441">
+      <c r="I4" s="126">
         <v>523953410</v>
       </c>
     </row>
@@ -9653,10 +9653,10 @@
       <c r="E5">
         <v>55432</v>
       </c>
-      <c r="H5" s="440" t="s">
+      <c r="H5" s="125" t="s">
         <v>236</v>
       </c>
-      <c r="I5" s="442">
+      <c r="I5" s="127">
         <v>59642884</v>
       </c>
     </row>
